--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46227.735758333336</v>
+        <v>46230.73821841435</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>42</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="296">
   <si>
     <t>50001576- "XEMORTIZ FIRST MAJESTIC"</t>
   </si>
@@ -394,28 +394,34 @@
     <t>Plano Preliminar OT 4375</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Plano Definitivos OT 4375</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1216762846409976</t>
+  </si>
+  <si>
+    <t>Plano Definitivos OT 4375</t>
+  </si>
+  <si>
+    <t>Check Planos OT 4375,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1216762846410001</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Plano Definitivos OT 4375</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>1216762846409976</t>
-  </si>
-  <si>
-    <t>Plano Definitivos OT 4375</t>
-  </si>
-  <si>
-    <t>Check Planos OT 4375,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1216762846410001</t>
   </si>
   <si>
     <t>Propuesta Fabricación externa   OT 4375,Propuesta Mecanizado OT 4375,Propuesta Corte plasma  OT 4375,propuesta Corte laser OT 4375,Ingenieria y diseñoo:,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
@@ -3308,7 +3314,7 @@
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46227.19181289352</v>
+        <v>46231.54203935185</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>126</v>
@@ -3371,7 +3377,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46224.88641827546</v>
+        <v>46231.54209966435</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>132</v>
@@ -3443,10 +3449,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I37" s="9">
         <v>46244</v>
@@ -3470,7 +3476,7 @@
         <v>132</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9">
         <v>46244</v>
@@ -3490,7 +3496,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46224.691245740745</v>
@@ -3500,16 +3506,16 @@
         <v>46224.8865816551</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I38" s="5">
         <v>46290</v>
@@ -3530,7 +3536,7 @@
         <v>123</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>123</v>
@@ -3553,7 +3559,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B39" s="9">
         <v>46224.6912528588</v>
@@ -3563,16 +3569,16 @@
         <v>46224.88666928241</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="9">
@@ -3588,13 +3594,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3604,7 +3610,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46224.691256886574</v>
@@ -3614,16 +3620,16 @@
         <v>46224.88666613426</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3639,13 +3645,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3655,7 +3661,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B41" s="9">
         <v>46224.69128170139</v>
@@ -3665,16 +3671,16 @@
         <v>46224.886662986115</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="9">
@@ -3690,13 +3696,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3706,7 +3712,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B42" s="5">
         <v>46224.69139119213</v>
@@ -3716,7 +3722,7 @@
         <v>46224.824914756944</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3740,7 +3746,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3753,7 +3759,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B43" s="9">
         <v>46224.69139565973</v>
@@ -3763,16 +3769,16 @@
         <v>46224.88680275463</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I43" s="9">
         <v>46260</v>
@@ -3790,13 +3796,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>88</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q43" s="9">
         <v>46260</v>
@@ -3816,7 +3822,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46224.69140096065</v>
@@ -3826,16 +3832,16 @@
         <v>46224.88679966435</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I44" s="5">
         <v>46260</v>
@@ -3853,13 +3859,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="5">
         <v>46260</v>
@@ -3879,7 +3885,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B45" s="9">
         <v>46224.69140581018</v>
@@ -3889,16 +3895,16 @@
         <v>46224.886796192135</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I45" s="9">
         <v>46260</v>
@@ -3916,13 +3922,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>104</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q45" s="9">
         <v>46260</v>
@@ -3942,7 +3948,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B46" s="5">
         <v>46224.691410740736</v>
@@ -3952,7 +3958,7 @@
         <v>46224.88687898148</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -3979,13 +3985,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q46" s="5">
         <v>46261</v>
@@ -4005,7 +4011,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B47" s="9">
         <v>46224.69141809028</v>
@@ -4015,7 +4021,7 @@
         <v>46224.886876122684</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
@@ -4042,13 +4048,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="9">
         <v>46261</v>
@@ -4068,7 +4074,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46224.69142430555</v>
@@ -4078,7 +4084,7 @@
         <v>46224.88687315972</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4105,13 +4111,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="5">
         <v>46261</v>
@@ -4131,7 +4137,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B49" s="9">
         <v>46224.69143046296</v>
@@ -4141,7 +4147,7 @@
         <v>46224.835371608795</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4165,7 +4171,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4178,7 +4184,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46224.6914341088</v>
@@ -4194,10 +4200,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I50" s="5">
         <v>46262</v>
@@ -4215,13 +4221,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q50" s="5">
         <v>46266</v>
@@ -4241,7 +4247,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B51" s="9">
         <v>46224.69144137732</v>
@@ -4257,10 +4263,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I51" s="9">
         <v>46267</v>
@@ -4278,13 +4284,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q51" s="9">
         <v>46273</v>
@@ -4304,7 +4310,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B52" s="5">
         <v>46224.69144840278</v>
@@ -4314,16 +4320,16 @@
         <v>46224.887152905096</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I52" s="5">
         <v>46267</v>
@@ -4344,10 +4350,10 @@
         <v>116</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4357,7 +4363,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B53" s="9">
         <v>46224.691457141205</v>
@@ -4367,16 +4373,16 @@
         <v>46224.88714986111</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I53" s="9">
         <v>46267</v>
@@ -4397,10 +4403,10 @@
         <v>116</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4410,7 +4416,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B54" s="5">
         <v>46224.69146548611</v>
@@ -4420,16 +4426,16 @@
         <v>46224.88714690972</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I54" s="5">
         <v>46267</v>
@@ -4450,10 +4456,10 @@
         <v>116</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4463,7 +4469,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B55" s="9">
         <v>46224.691625312495</v>
@@ -4473,16 +4479,16 @@
         <v>46224.88734793982</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I55" s="9">
         <v>46274</v>
@@ -4500,13 +4506,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q55" s="9">
         <v>46274</v>
@@ -4526,7 +4532,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B56" s="5">
         <v>46224.69163763888</v>
@@ -4536,16 +4542,16 @@
         <v>46224.88729486111</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I56" s="5">
         <v>46274</v>
@@ -4563,13 +4569,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4579,7 +4585,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B57" s="9">
         <v>46224.69164405092</v>
@@ -4589,16 +4595,16 @@
         <v>46224.88729221065</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I57" s="9">
         <v>46274</v>
@@ -4616,13 +4622,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4632,7 +4638,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B58" s="5">
         <v>46224.69164984954</v>
@@ -4642,16 +4648,16 @@
         <v>46224.88728945602</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I58" s="5">
         <v>46274</v>
@@ -4669,13 +4675,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4685,7 +4691,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B59" s="9">
         <v>46224.69178202546</v>
@@ -4695,7 +4701,7 @@
         <v>46224.83612613426</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -4719,7 +4725,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -4732,26 +4738,26 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B60" s="5">
         <v>46224.691786446754</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46224.88755170139</v>
+        <v>46231.171597974535</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I60" s="5">
         <v>46230</v>
@@ -4769,13 +4775,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>50</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q60" s="5">
         <v>46231</v>
@@ -4795,26 +4801,26 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B61" s="9">
         <v>46224.69179621528</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46224.887548645835</v>
+        <v>46231.17160611111</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I61" s="9">
         <v>46230</v>
@@ -4832,13 +4838,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q61" s="9">
         <v>46231</v>
@@ -4858,26 +4864,26 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B62" s="5">
         <v>46224.691807152776</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46224.88754401621</v>
+        <v>46231.17160744213</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I62" s="5">
         <v>46230</v>
@@ -4895,13 +4901,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>59</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q62" s="5">
         <v>46231</v>
@@ -4921,7 +4927,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B63" s="9">
         <v>46224.69181694444</v>
@@ -4931,7 +4937,7 @@
         <v>46224.878543969906</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>25</v>
@@ -4955,7 +4961,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -4968,7 +4974,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B64" s="5">
         <v>46224.69182049768</v>
@@ -4978,7 +4984,7 @@
         <v>46224.887708587965</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5005,13 +5011,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q64" s="5">
         <v>46281</v>
@@ -5031,7 +5037,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B65" s="9">
         <v>46224.691826967595</v>
@@ -5041,7 +5047,7 @@
         <v>46224.887663622685</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5068,13 +5074,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5084,7 +5090,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B66" s="5">
         <v>46224.691831840275</v>
@@ -5094,7 +5100,7 @@
         <v>46224.8876609375</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5121,13 +5127,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5137,7 +5143,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B67" s="9">
         <v>46224.69183667824</v>
@@ -5147,7 +5153,7 @@
         <v>46224.8876578125</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5174,13 +5180,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5190,7 +5196,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B68" s="5">
         <v>46224.69195275463</v>
@@ -5200,7 +5206,7 @@
         <v>46224.88781885417</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5227,13 +5233,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q68" s="5">
         <v>46286</v>
@@ -5253,7 +5259,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B69" s="9">
         <v>46224.69195878472</v>
@@ -5263,7 +5269,7 @@
         <v>46224.888011284726</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5290,13 +5296,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5306,7 +5312,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B70" s="5">
         <v>46224.69196560185</v>
@@ -5316,7 +5322,7 @@
         <v>46224.88800827546</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5343,13 +5349,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5359,7 +5365,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B71" s="9">
         <v>46224.69197195602</v>
@@ -5369,7 +5375,7 @@
         <v>46224.888004699074</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5396,13 +5402,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5412,7 +5418,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B72" s="5">
         <v>46224.6920590625</v>
@@ -5422,7 +5428,7 @@
         <v>46224.88781516204</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5449,13 +5455,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q72" s="5">
         <v>46287</v>
@@ -5475,7 +5481,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B73" s="9">
         <v>46224.69206486111</v>
@@ -5485,7 +5491,7 @@
         <v>46224.888117256945</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5512,13 +5518,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5528,7 +5534,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B74" s="5">
         <v>46224.69207089121</v>
@@ -5538,7 +5544,7 @@
         <v>46224.88811447917</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5565,13 +5571,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5581,7 +5587,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B75" s="9">
         <v>46224.69207630787</v>
@@ -5591,7 +5597,7 @@
         <v>46224.88811143518</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5618,13 +5624,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5634,7 +5640,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B76" s="5">
         <v>46224.692210925925</v>
@@ -5644,7 +5650,7 @@
         <v>46224.88781181713</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5671,13 +5677,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q76" s="5">
         <v>46288</v>
@@ -5697,7 +5703,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B77" s="9">
         <v>46224.69221851852</v>
@@ -5707,7 +5713,7 @@
         <v>46224.88822145833</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5734,13 +5740,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5750,7 +5756,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B78" s="5">
         <v>46224.692225335646</v>
@@ -5760,7 +5766,7 @@
         <v>46224.88821883102</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5787,13 +5793,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5803,7 +5809,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B79" s="9">
         <v>46224.69223655092</v>
@@ -5813,7 +5819,7 @@
         <v>46224.88821421296</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -5840,13 +5846,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -5856,7 +5862,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B80" s="5">
         <v>46224.69235351852</v>
@@ -5866,7 +5872,7 @@
         <v>46224.887808576386</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -5893,13 +5899,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q80" s="5">
         <v>46289</v>
@@ -5919,7 +5925,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B81" s="9">
         <v>46224.6923596875</v>
@@ -5929,7 +5935,7 @@
         <v>46224.88831505787</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -5956,13 +5962,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -5972,7 +5978,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B82" s="5">
         <v>46224.69236840278</v>
@@ -5982,7 +5988,7 @@
         <v>46224.88831152778</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6009,13 +6015,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6025,7 +6031,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B83" s="9">
         <v>46224.69237796296</v>
@@ -6035,7 +6041,7 @@
         <v>46224.88830864584</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6062,13 +6068,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6078,7 +6084,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B84" s="5">
         <v>46224.69253115741</v>
@@ -6088,7 +6094,7 @@
         <v>46224.88780266204</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6115,13 +6121,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q84" s="5">
         <v>46293</v>
@@ -6141,7 +6147,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B85" s="9">
         <v>46224.69253806713</v>
@@ -6151,7 +6157,7 @@
         <v>46224.88840122685</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6176,13 +6182,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6192,7 +6198,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B86" s="5">
         <v>46224.69254259259</v>
@@ -6202,7 +6208,7 @@
         <v>46224.88839846065</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6227,13 +6233,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6243,7 +6249,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B87" s="9">
         <v>46224.69254695602</v>
@@ -6253,7 +6259,7 @@
         <v>46224.888395601854</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6278,13 +6284,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6294,7 +6300,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B88" s="5">
         <v>46224.69261697917</v>
@@ -6304,7 +6310,7 @@
         <v>46224.88265856481</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>25</v>
@@ -6328,7 +6334,7 @@
         <v>26</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -6341,7 +6347,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B89" s="9">
         <v>46224.69265170139</v>
@@ -6351,16 +6357,16 @@
         <v>46224.888549525465</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I89" s="9">
         <v>46294</v>
@@ -6378,13 +6384,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q89" s="9">
         <v>46294</v>
@@ -6404,7 +6410,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B90" s="5">
         <v>46224.69265774306</v>
@@ -6414,16 +6420,16 @@
         <v>46224.88851116898</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I90" s="5">
         <v>46294</v>
@@ -6441,13 +6447,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6457,7 +6463,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B91" s="9">
         <v>46224.69266123843</v>
@@ -6467,16 +6473,16 @@
         <v>46224.8885084838</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I91" s="9">
         <v>46294</v>
@@ -6494,13 +6500,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6510,7 +6516,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B92" s="5">
         <v>46224.692664456015</v>
@@ -6520,16 +6526,16 @@
         <v>46224.88850347222</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I92" s="5">
         <v>46294</v>
@@ -6547,13 +6553,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6563,7 +6569,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B93" s="9">
         <v>46224.69271221065</v>
@@ -6573,7 +6579,7 @@
         <v>46224.88867554398</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6600,13 +6606,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q93" s="9">
         <v>46295</v>
@@ -6626,7 +6632,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B94" s="5">
         <v>46224.69271712963</v>
@@ -6636,7 +6642,7 @@
         <v>46224.888643495375</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6661,13 +6667,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6677,7 +6683,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B95" s="9">
         <v>46224.692723113425</v>
@@ -6687,7 +6693,7 @@
         <v>46224.88864100694</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6712,13 +6718,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6728,7 +6734,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B96" s="5">
         <v>46224.692728483795</v>
@@ -6738,7 +6744,7 @@
         <v>46224.88863769676</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6763,13 +6769,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6779,7 +6785,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B97" s="9">
         <v>46224.692771875</v>
@@ -6789,16 +6795,16 @@
         <v>46224.88885393519</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I97" s="9">
         <v>46296</v>
@@ -6816,13 +6822,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q97" s="9">
         <v>46296</v>
@@ -6842,7 +6848,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B98" s="5">
         <v>46224.69280849537</v>
@@ -6852,16 +6858,16 @@
         <v>46224.88880863426</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I98" s="5">
         <v>46296</v>
@@ -6879,13 +6885,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -6895,7 +6901,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B99" s="9">
         <v>46224.69281277778</v>
@@ -6905,16 +6911,16 @@
         <v>46224.888805462964</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I99" s="9">
         <v>46296</v>
@@ -6932,13 +6938,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -6948,7 +6954,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B100" s="5">
         <v>46224.69281645834</v>
@@ -6958,16 +6964,16 @@
         <v>46224.88880255787</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I100" s="5">
         <v>46296</v>
@@ -6985,13 +6991,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7001,7 +7007,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B101" s="9">
         <v>46224.692877442125</v>
@@ -7011,16 +7017,16 @@
         <v>46224.88918993056</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I101" s="9">
         <v>46297</v>
@@ -7038,13 +7044,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q101" s="9">
         <v>46297</v>
@@ -7064,7 +7070,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B102" s="5">
         <v>46224.69288434028</v>
@@ -7074,16 +7080,16 @@
         <v>46224.88913273148</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I102" s="5">
         <v>46297</v>
@@ -7101,13 +7107,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7117,7 +7123,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B103" s="9">
         <v>46224.69288743056</v>
@@ -7127,16 +7133,16 @@
         <v>46224.8891297338</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I103" s="9">
         <v>46297</v>
@@ -7154,13 +7160,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7170,7 +7176,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B104" s="5">
         <v>46224.692890509265</v>
@@ -7180,16 +7186,16 @@
         <v>46224.88912665509</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I104" s="5">
         <v>46297</v>
@@ -7207,13 +7213,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7223,7 +7229,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B105" s="9">
         <v>46224.692977743056</v>
@@ -7233,7 +7239,7 @@
         <v>46224.88292137731</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>25</v>
@@ -7257,7 +7263,7 @@
         <v>26</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>26</v>
@@ -7270,7 +7276,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B106" s="5">
         <v>46224.69298071759</v>
@@ -7280,16 +7286,16 @@
         <v>46224.88926996528</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I106" s="5">
         <v>46300</v>
@@ -7307,13 +7313,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q106" s="5">
         <v>46304</v>
@@ -7333,7 +7339,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B107" s="9">
         <v>46224.693000983796</v>
@@ -7343,7 +7349,7 @@
         <v>46224.88933664352</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7370,13 +7376,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q107" s="9">
         <v>46304</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="307">
   <si>
     <t>50001576- "XEMORTIZ FIRST MAJESTIC"</t>
   </si>
@@ -118,6 +118,31 @@
     <t>Alcance del proyecto</t>
   </si>
   <si>
+    <t xml:space="preserve">Buen día,
+Para el pedido 1576 se tienen 3 ventiladores ZVN 1-9-86/2 para Xemortiz (First Majestic):
+    Planos para fabricación O/4375:
+        Ventilador ZVN 1-9-86/2 con motor WEG
+        Alcance: Tobera + Rejilla Concretica + Tipo A 900mm
+    Selección de Rodete:
+        Rodete de placas s/plano 4999.00
+        Alabe s/ plano 4999.01
+        Z8 N590
+        Código 300000
+        hgutierrez@zitron.com, tu apoyo con la definición de calaje.
+    Tratamiento superficial estándar Zitron:
+        Preparación de superficie: Arenado SSPC-SP10
+        1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+    Datos eléctricos para el motor:
+        Motor WEG 86 kW, 2 Polos, FR 250.
+        Código: 350010
+        460 VAC, 60 Hz, IEC-IE3, IP55, FS 1.0.-
+        Se debe considerar duplicado de placas.
+    Fecha de entrega: 04-08-2026
+Quedo atenta
+Saludos,</t>
+  </si>
+  <si>
     <t>1216763049714883</t>
   </si>
   <si>
@@ -148,36 +173,36 @@
     <t>Plano Preliminar OT 4375,Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
+    <t>1216730497556441</t>
+  </si>
+  <si>
+    <t>Reservas</t>
+  </si>
+  <si>
+    <t>Reserva Alabes OT 4375,Reserva rodete OT 4375,Reserva motor  OT 4375</t>
+  </si>
+  <si>
+    <t>1216730497556447</t>
+  </si>
+  <si>
+    <t>Reserva Alabes OT 4375</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
+    <t>Reservas,Recepcion Alabe OT 4375</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1216730497556441</t>
-  </si>
-  <si>
-    <t>Reservas</t>
-  </si>
-  <si>
-    <t>Reserva Alabes OT 4375,Reserva rodete OT 4375,Reserva motor  OT 4375</t>
-  </si>
-  <si>
-    <t>1216730497556447</t>
-  </si>
-  <si>
-    <t>Reserva Alabes OT 4375</t>
-  </si>
-  <si>
-    <t>NATALYA ESPINOZA</t>
-  </si>
-  <si>
-    <t>nespinoza@zitron.com</t>
-  </si>
-  <si>
-    <t>Reservas,Recepcion Alabe OT 4375</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
     <t>1216730497556448</t>
   </si>
   <si>
@@ -640,7 +665,19 @@
     <t>Montaje:</t>
   </si>
   <si>
-    <t>RE-PINTADO OT 4375,Montaje Rodete OT 4375,Montaje motor OT 4375,Montaje Alabe OT 4375,Revestimiento OT 4375,Pruebas FAT OT 4375</t>
+    <t>Montaje Rodete OT 4375,Montaje motor OT 4375,Montaje Alabe OT 4375,Revestimiento OT 4375</t>
+  </si>
+  <si>
+    <t>1216991344494299</t>
+  </si>
+  <si>
+    <t>Conexión eléctrica OT 4375</t>
+  </si>
+  <si>
+    <t>Montaje motor OT 4375</t>
+  </si>
+  <si>
+    <t>Pruebas FAT OT 4375</t>
   </si>
   <si>
     <t>1216763090891690</t>
@@ -649,6 +686,9 @@
     <t>Revestimiento OT 4375</t>
   </si>
   <si>
+    <t>Montaje:,Montaje Alabe OT 4375</t>
+  </si>
+  <si>
     <t>1216762727729087</t>
   </si>
   <si>
@@ -670,6 +710,12 @@
     <t>Montaje Alabe OT 4375</t>
   </si>
   <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Revestimiento OT 4375</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje Rodete OT 4375</t>
+  </si>
+  <si>
     <t>1216763050389900</t>
   </si>
   <si>
@@ -697,6 +743,12 @@
     <t>Montaje Rodete OT 4375</t>
   </si>
   <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Montaje Alabe OT 4375</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje motor OT 4375</t>
+  </si>
+  <si>
     <t>1216762959307831</t>
   </si>
   <si>
@@ -718,7 +770,10 @@
     <t>1216762959410712</t>
   </si>
   <si>
-    <t>Montaje motor OT 4375</t>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Montaje Rodete OT 4375</t>
+  </si>
+  <si>
+    <t>Montaje:,Conexión eléctrica OT 4375</t>
   </si>
   <si>
     <t>1216762959410727</t>
@@ -745,7 +800,10 @@
     <t>1216763091386830</t>
   </si>
   <si>
-    <t>Pruebas FAT OT 4375</t>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Conexión eléctrica OT 4375</t>
+  </si>
+  <si>
+    <t>RE-PINTADO OT 4375</t>
   </si>
   <si>
     <t>1216763091401629</t>
@@ -763,10 +821,10 @@
     <t>1216763160154039</t>
   </si>
   <si>
-    <t>RE-PINTADO OT 4375</t>
-  </si>
-  <si>
-    <t>Montaje:,Coordinacion Entrega con Cliente OT 4375</t>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Pruebas FAT OT 4375</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente OT 4375</t>
   </si>
   <si>
     <t>1216762728208417</t>
@@ -791,9 +849,6 @@
   </si>
   <si>
     <t>1216762959483284</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente OT 4375</t>
   </si>
   <si>
     <t>Karin Pinto</t>
@@ -967,12 +1022,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -1422,7 +1477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U107"/>
+  <dimension ref="A1:U108"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -1647,7 +1702,7 @@
         <v>46227.58879861111</v>
       </c>
       <c r="D6" s="5">
-        <v>46227.58892072916</v>
+        <v>46232.53769077546</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1669,7 +1724,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -1701,7 +1756,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="9">
         <v>46224.69100291667</v>
@@ -1713,7 +1768,7 @@
         <v>46227.58883761574</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>26</v>
@@ -1744,7 +1799,7 @@
         <v>26</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q7" s="9">
         <v>46134</v>
@@ -1764,7 +1819,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="5">
         <v>46224.69100611111</v>
@@ -1776,7 +1831,7 @@
         <v>46227.58892084491</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
@@ -1827,17 +1882,19 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="9">
         <v>46224.69092476852</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="9">
+        <v>46232.537968819444</v>
+      </c>
       <c r="D9" s="9">
-        <v>46224.7271350463</v>
+        <v>46232.53798356482</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>25</v>
@@ -1861,7 +1918,7 @@
         <v>26</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P9" s="10" t="s">
         <v>26</v>
@@ -1869,22 +1926,28 @@
       <c r="Q9" s="10"/>
       <c r="R9" s="10"/>
       <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10"/>
+      <c r="T9" s="10">
+        <v>1</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="5">
         <v>46224.69102</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46232.53794899306</v>
+      </c>
       <c r="D10" s="5">
-        <v>46230.73821841435</v>
+        <v>46232.53796836805</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>26</v>
@@ -1905,19 +1968,19 @@
         <v>26</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q10" s="5">
         <v>46136</v>
@@ -1929,10 +1992,10 @@
         <v>32</v>
       </c>
       <c r="T10" s="6">
-        <v>0</v>
-      </c>
-      <c r="U10" s="11" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -2024,7 +2087,7 @@
         <v>47</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>53</v>
@@ -2035,19 +2098,19 @@
       <c r="R12" s="5">
         <v>46226</v>
       </c>
-      <c r="S12" s="12" t="s">
+      <c r="S12" s="11" t="s">
         <v>54</v>
       </c>
       <c r="T12" s="6">
         <v>0</v>
       </c>
-      <c r="U12" s="11" t="s">
-        <v>45</v>
+      <c r="U12" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B13" s="9">
         <v>46224.69724422454</v>
@@ -2057,7 +2120,7 @@
         <v>46228.16880770834</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
@@ -2087,10 +2150,10 @@
         <v>47</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q13" s="9">
         <v>46227</v>
@@ -2098,19 +2161,19 @@
       <c r="R13" s="9">
         <v>46226</v>
       </c>
-      <c r="S13" s="12" t="s">
+      <c r="S13" s="11" t="s">
         <v>54</v>
       </c>
       <c r="T13" s="10">
         <v>0</v>
       </c>
-      <c r="U13" s="11" t="s">
-        <v>45</v>
+      <c r="U13" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" s="5">
         <v>46224.69937288194</v>
@@ -2120,7 +2183,7 @@
         <v>46228.16880583334</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2150,10 +2213,10 @@
         <v>47</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q14" s="5">
         <v>46227</v>
@@ -2161,19 +2224,19 @@
       <c r="R14" s="5">
         <v>46226</v>
       </c>
-      <c r="S14" s="12" t="s">
+      <c r="S14" s="11" t="s">
         <v>54</v>
       </c>
       <c r="T14" s="6">
         <v>0</v>
       </c>
-      <c r="U14" s="11" t="s">
-        <v>45</v>
+      <c r="U14" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" s="9">
         <v>46224.69093027778</v>
@@ -2183,7 +2246,7 @@
         <v>46224.727983634264</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>25</v>
@@ -2207,7 +2270,7 @@
         <v>26</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P15" s="10" t="s">
         <v>26</v>
@@ -2220,7 +2283,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" s="5">
         <v>46224.69104479167</v>
@@ -2230,7 +2293,7 @@
         <v>46224.88546868056</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2257,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q16" s="5">
         <v>46246</v>
@@ -2277,13 +2340,13 @@
       <c r="T16" s="6">
         <v>0</v>
       </c>
-      <c r="U16" s="12" t="s">
-        <v>67</v>
+      <c r="U16" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" s="9">
         <v>46224.691050636575</v>
@@ -2293,7 +2356,7 @@
         <v>46224.88546538194</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2320,13 +2383,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q17" s="9">
         <v>46246</v>
@@ -2340,13 +2403,13 @@
       <c r="T17" s="10">
         <v>0</v>
       </c>
-      <c r="U17" s="12" t="s">
-        <v>67</v>
+      <c r="U17" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B18" s="5">
         <v>46224.691053912036</v>
@@ -2356,7 +2419,7 @@
         <v>46224.88546251158</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2383,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q18" s="5">
         <v>46246</v>
@@ -2403,13 +2466,13 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="12" t="s">
-        <v>67</v>
+      <c r="U18" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B19" s="9">
         <v>46224.69105851852</v>
@@ -2419,7 +2482,7 @@
         <v>46224.88545775463</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2446,13 +2509,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q19" s="9">
         <v>46246</v>
@@ -2466,13 +2529,13 @@
       <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="12" t="s">
-        <v>67</v>
+      <c r="U19" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B20" s="5">
         <v>46224.69093564815</v>
@@ -2482,7 +2545,7 @@
         <v>46224.72969400463</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2506,7 +2569,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2519,7 +2582,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" s="9">
         <v>46224.69110914352</v>
@@ -2529,16 +2592,16 @@
         <v>46224.88562534722</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I21" s="9">
         <v>46248</v>
@@ -2556,13 +2619,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q21" s="9">
         <v>46259</v>
@@ -2576,13 +2639,13 @@
       <c r="T21" s="10">
         <v>0</v>
       </c>
-      <c r="U21" s="12" t="s">
-        <v>67</v>
+      <c r="U21" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B22" s="5">
         <v>46224.691113368055</v>
@@ -2592,16 +2655,16 @@
         <v>46224.88573403935</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I22" s="5">
         <v>46247</v>
@@ -2619,13 +2682,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
@@ -2635,13 +2698,13 @@
       <c r="T22" s="6">
         <v>0</v>
       </c>
-      <c r="U22" s="12" t="s">
-        <v>67</v>
+      <c r="U22" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" s="9">
         <v>46224.69111763889</v>
@@ -2651,16 +2714,16 @@
         <v>46224.885731030095</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I23" s="9">
         <v>46251</v>
@@ -2678,13 +2741,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2694,13 +2757,13 @@
       <c r="T23" s="10">
         <v>0</v>
       </c>
-      <c r="U23" s="12" t="s">
-        <v>67</v>
+      <c r="U23" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" s="5">
         <v>46224.691122118056</v>
@@ -2710,16 +2773,16 @@
         <v>46224.88562246528</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I24" s="5">
         <v>46248</v>
@@ -2737,10 +2800,10 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2757,13 +2820,13 @@
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="12" t="s">
-        <v>67</v>
+      <c r="U24" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B25" s="9">
         <v>46224.69117694444</v>
@@ -2773,16 +2836,16 @@
         <v>46224.88583665509</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I25" s="9">
         <v>46247</v>
@@ -2800,13 +2863,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2816,7 +2879,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B26" s="5">
         <v>46224.691182546296</v>
@@ -2826,16 +2889,16 @@
         <v>46224.88583366898</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I26" s="5">
         <v>46251</v>
@@ -2853,13 +2916,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2869,7 +2932,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B27" s="9">
         <v>46224.69118782408</v>
@@ -2879,16 +2942,16 @@
         <v>46224.88561925926</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I27" s="9">
         <v>46248</v>
@@ -2906,10 +2969,10 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -2926,13 +2989,13 @@
       <c r="T27" s="10">
         <v>0</v>
       </c>
-      <c r="U27" s="12" t="s">
-        <v>67</v>
+      <c r="U27" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B28" s="5">
         <v>46224.69119221065</v>
@@ -2942,16 +3005,16 @@
         <v>46224.88591563657</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -2969,13 +3032,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -2985,7 +3048,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B29" s="9">
         <v>46224.69119738426</v>
@@ -2995,16 +3058,16 @@
         <v>46224.88591252315</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I29" s="9">
         <v>46251</v>
@@ -3022,13 +3085,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3038,7 +3101,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B30" s="5">
         <v>46224.72969201389</v>
@@ -3048,16 +3111,16 @@
         <v>46224.88605396991</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I30" s="5">
         <v>46260</v>
@@ -3075,10 +3138,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3095,13 +3158,13 @@
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="12" t="s">
-        <v>67</v>
+      <c r="U30" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31" s="9">
         <v>46224.72978952546</v>
@@ -3111,16 +3174,16 @@
         <v>46224.88615795139</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3138,13 +3201,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3154,7 +3217,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5">
         <v>46224.72983336805</v>
@@ -3164,16 +3227,16 @@
         <v>46224.886155405096</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I32" s="5">
         <v>46258</v>
@@ -3191,13 +3254,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3207,7 +3270,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B33" s="9">
         <v>46224.72985208333</v>
@@ -3217,16 +3280,16 @@
         <v>46224.88628099537</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I33" s="9">
         <v>46289</v>
@@ -3244,13 +3307,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3260,17 +3323,17 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5">
         <v>46224.690940555556</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46224.876093495375</v>
+        <v>46232.5743990162</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>25</v>
@@ -3294,7 +3357,7 @@
         <v>26</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3307,26 +3370,28 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B35" s="9">
         <v>46224.6912024537</v>
       </c>
-      <c r="C35" s="10"/>
+      <c r="C35" s="9">
+        <v>46232.574391863425</v>
+      </c>
       <c r="D35" s="9">
-        <v>46231.54203935185</v>
+        <v>46232.57441003472</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I35" s="9">
         <v>46230</v>
@@ -3344,13 +3409,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q35" s="9">
         <v>46234</v>
@@ -3358,38 +3423,38 @@
       <c r="R35" s="9">
         <v>46230</v>
       </c>
-      <c r="S35" s="11" t="s">
-        <v>130</v>
+      <c r="S35" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="T35" s="10">
-        <v>0</v>
-      </c>
-      <c r="U35" s="12" t="s">
-        <v>67</v>
+        <v>1</v>
+      </c>
+      <c r="U35" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46224.69120917824</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46231.54209966435</v>
+        <v>46232.57441020833</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46237</v>
@@ -3407,13 +3472,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="5">
         <v>46241</v>
@@ -3428,12 +3493,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="12" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="9">
         <v>46224.69121665509</v>
@@ -3443,16 +3508,16 @@
         <v>46224.88641491898</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I37" s="9">
         <v>46244</v>
@@ -3470,13 +3535,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="9">
         <v>46244</v>
@@ -3490,13 +3555,13 @@
       <c r="T37" s="10">
         <v>0</v>
       </c>
-      <c r="U37" s="12" t="s">
-        <v>67</v>
+      <c r="U37" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46224.691245740745</v>
@@ -3506,16 +3571,16 @@
         <v>46224.8865816551</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I38" s="5">
         <v>46290</v>
@@ -3533,13 +3598,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q38" s="5">
         <v>46290</v>
@@ -3553,13 +3618,13 @@
       <c r="T38" s="6">
         <v>0</v>
       </c>
-      <c r="U38" s="12" t="s">
-        <v>67</v>
+      <c r="U38" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="9">
         <v>46224.6912528588</v>
@@ -3569,16 +3634,16 @@
         <v>46224.88666928241</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="9">
@@ -3594,13 +3659,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3610,7 +3675,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46224.691256886574</v>
@@ -3620,16 +3685,16 @@
         <v>46224.88666613426</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3645,13 +3710,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3661,7 +3726,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B41" s="9">
         <v>46224.69128170139</v>
@@ -3671,16 +3736,16 @@
         <v>46224.886662986115</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="9">
@@ -3696,13 +3761,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3712,7 +3777,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B42" s="5">
         <v>46224.69139119213</v>
@@ -3722,7 +3787,7 @@
         <v>46224.824914756944</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3746,7 +3811,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3759,7 +3824,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B43" s="9">
         <v>46224.69139565973</v>
@@ -3769,16 +3834,16 @@
         <v>46224.88680275463</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I43" s="9">
         <v>46260</v>
@@ -3796,13 +3861,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q43" s="9">
         <v>46260</v>
@@ -3816,13 +3881,13 @@
       <c r="T43" s="10">
         <v>0</v>
       </c>
-      <c r="U43" s="12" t="s">
-        <v>67</v>
+      <c r="U43" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B44" s="5">
         <v>46224.69140096065</v>
@@ -3832,16 +3897,16 @@
         <v>46224.88679966435</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I44" s="5">
         <v>46260</v>
@@ -3859,13 +3924,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q44" s="5">
         <v>46260</v>
@@ -3879,13 +3944,13 @@
       <c r="T44" s="6">
         <v>0</v>
       </c>
-      <c r="U44" s="12" t="s">
-        <v>67</v>
+      <c r="U44" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B45" s="9">
         <v>46224.69140581018</v>
@@ -3895,16 +3960,16 @@
         <v>46224.886796192135</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I45" s="9">
         <v>46260</v>
@@ -3922,13 +3987,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q45" s="9">
         <v>46260</v>
@@ -3942,13 +4007,13 @@
       <c r="T45" s="10">
         <v>0</v>
       </c>
-      <c r="U45" s="12" t="s">
-        <v>67</v>
+      <c r="U45" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B46" s="5">
         <v>46224.691410740736</v>
@@ -3958,16 +4023,16 @@
         <v>46224.88687898148</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I46" s="5">
         <v>46261</v>
@@ -3985,13 +4050,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q46" s="5">
         <v>46261</v>
@@ -4005,13 +4070,13 @@
       <c r="T46" s="6">
         <v>0</v>
       </c>
-      <c r="U46" s="12" t="s">
-        <v>67</v>
+      <c r="U46" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B47" s="9">
         <v>46224.69141809028</v>
@@ -4021,16 +4086,16 @@
         <v>46224.886876122684</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I47" s="9">
         <v>46261</v>
@@ -4048,13 +4113,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="9">
         <v>46261</v>
@@ -4068,13 +4133,13 @@
       <c r="T47" s="10">
         <v>0</v>
       </c>
-      <c r="U47" s="12" t="s">
-        <v>67</v>
+      <c r="U47" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B48" s="5">
         <v>46224.69142430555</v>
@@ -4084,16 +4149,16 @@
         <v>46224.88687315972</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4111,13 +4176,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q48" s="5">
         <v>46261</v>
@@ -4131,13 +4196,13 @@
       <c r="T48" s="6">
         <v>0</v>
       </c>
-      <c r="U48" s="12" t="s">
-        <v>67</v>
+      <c r="U48" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B49" s="9">
         <v>46224.69143046296</v>
@@ -4147,7 +4212,7 @@
         <v>46224.835371608795</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4171,7 +4236,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4184,7 +4249,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46224.6914341088</v>
@@ -4194,16 +4259,16 @@
         <v>46224.88693119213</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I50" s="5">
         <v>46262</v>
@@ -4221,13 +4286,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q50" s="5">
         <v>46266</v>
@@ -4241,13 +4306,13 @@
       <c r="T50" s="6">
         <v>0</v>
       </c>
-      <c r="U50" s="12" t="s">
-        <v>67</v>
+      <c r="U50" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B51" s="9">
         <v>46224.69144137732</v>
@@ -4257,16 +4322,16 @@
         <v>46224.887193206014</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I51" s="9">
         <v>46267</v>
@@ -4284,13 +4349,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q51" s="9">
         <v>46273</v>
@@ -4304,13 +4369,13 @@
       <c r="T51" s="10">
         <v>0</v>
       </c>
-      <c r="U51" s="12" t="s">
-        <v>67</v>
+      <c r="U51" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B52" s="5">
         <v>46224.69144840278</v>
@@ -4320,16 +4385,16 @@
         <v>46224.887152905096</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I52" s="5">
         <v>46267</v>
@@ -4347,13 +4412,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4363,7 +4428,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B53" s="9">
         <v>46224.691457141205</v>
@@ -4373,16 +4438,16 @@
         <v>46224.88714986111</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I53" s="9">
         <v>46267</v>
@@ -4400,13 +4465,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4416,7 +4481,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46224.69146548611</v>
@@ -4426,16 +4491,16 @@
         <v>46224.88714690972</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I54" s="5">
         <v>46267</v>
@@ -4453,13 +4518,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4469,7 +4534,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B55" s="9">
         <v>46224.691625312495</v>
@@ -4479,16 +4544,16 @@
         <v>46224.88734793982</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I55" s="9">
         <v>46274</v>
@@ -4506,13 +4571,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q55" s="9">
         <v>46274</v>
@@ -4526,13 +4591,13 @@
       <c r="T55" s="10">
         <v>0</v>
       </c>
-      <c r="U55" s="12" t="s">
-        <v>67</v>
+      <c r="U55" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B56" s="5">
         <v>46224.69163763888</v>
@@ -4542,16 +4607,16 @@
         <v>46224.88729486111</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I56" s="5">
         <v>46274</v>
@@ -4569,13 +4634,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4585,7 +4650,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B57" s="9">
         <v>46224.69164405092</v>
@@ -4595,16 +4660,16 @@
         <v>46224.88729221065</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I57" s="9">
         <v>46274</v>
@@ -4622,13 +4687,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4638,7 +4703,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B58" s="5">
         <v>46224.69164984954</v>
@@ -4648,16 +4713,16 @@
         <v>46224.88728945602</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I58" s="5">
         <v>46274</v>
@@ -4675,13 +4740,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4691,7 +4756,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B59" s="9">
         <v>46224.69178202546</v>
@@ -4701,7 +4766,7 @@
         <v>46224.83612613426</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -4725,7 +4790,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -4738,26 +4803,26 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B60" s="5">
         <v>46224.691786446754</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46231.171597974535</v>
+        <v>46232.18045346065</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I60" s="5">
         <v>46230</v>
@@ -4775,13 +4840,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>50</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q60" s="5">
         <v>46231</v>
@@ -4789,38 +4854,38 @@
       <c r="R60" s="5">
         <v>46230</v>
       </c>
-      <c r="S60" s="7" t="s">
-        <v>32</v>
+      <c r="S60" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
-      <c r="U60" s="12" t="s">
-        <v>67</v>
+      <c r="U60" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B61" s="9">
         <v>46224.69179621528</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46231.17160611111</v>
+        <v>46232.1804544676</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I61" s="9">
         <v>46230</v>
@@ -4838,13 +4903,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q61" s="9">
         <v>46231</v>
@@ -4852,38 +4917,38 @@
       <c r="R61" s="9">
         <v>46230</v>
       </c>
-      <c r="S61" s="7" t="s">
-        <v>32</v>
+      <c r="S61" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
       </c>
-      <c r="U61" s="12" t="s">
-        <v>67</v>
+      <c r="U61" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B62" s="5">
         <v>46224.691807152776</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46231.17160744213</v>
+        <v>46232.18045403935</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I62" s="5">
         <v>46230</v>
@@ -4901,13 +4966,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q62" s="5">
         <v>46231</v>
@@ -4915,29 +4980,29 @@
       <c r="R62" s="5">
         <v>46230</v>
       </c>
-      <c r="S62" s="7" t="s">
-        <v>32</v>
+      <c r="S62" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
       </c>
-      <c r="U62" s="12" t="s">
-        <v>67</v>
+      <c r="U62" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B63" s="9">
         <v>46224.69181694444</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46224.878543969906</v>
+        <v>46232.60338635417</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>25</v>
@@ -4961,7 +5026,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -4974,32 +5039,30 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B64" s="5">
-        <v>46224.69182049768</v>
+        <v>46232.603311631945</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46224.887708587965</v>
+        <v>46232.62438241898</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>52</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H64" s="6"/>
       <c r="I64" s="5">
-        <v>46275</v>
+        <v>46289</v>
       </c>
       <c r="J64" s="5">
-        <v>46281</v>
+        <v>46289</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>26</v>
@@ -5011,43 +5074,33 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q64" s="5">
-        <v>46281</v>
-      </c>
-      <c r="R64" s="5">
-        <v>46275</v>
-      </c>
-      <c r="S64" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T64" s="6">
-        <v>0</v>
-      </c>
-      <c r="U64" s="12" t="s">
-        <v>67</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6"/>
+      <c r="T64" s="6"/>
+      <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B65" s="9">
-        <v>46224.691826967595</v>
+        <v>46224.69182049768</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46224.887663622685</v>
+        <v>46232.624381828704</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>144</v>
+        <v>216</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5074,33 +5127,43 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q65" s="10"/>
-      <c r="R65" s="10"/>
-      <c r="S65" s="10"/>
-      <c r="T65" s="10"/>
-      <c r="U65" s="10"/>
+        <v>217</v>
+      </c>
+      <c r="Q65" s="9">
+        <v>46281</v>
+      </c>
+      <c r="R65" s="9">
+        <v>46275</v>
+      </c>
+      <c r="S65" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T65" s="10">
+        <v>0</v>
+      </c>
+      <c r="U65" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B66" s="5">
-        <v>46224.691831840275</v>
+        <v>46224.691826967595</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46224.8876609375</v>
+        <v>46224.887663622685</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5127,13 +5190,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5143,17 +5206,17 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B67" s="9">
-        <v>46224.69183667824</v>
+        <v>46224.691831840275</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46224.8876578125</v>
+        <v>46224.8876609375</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5180,13 +5243,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5196,17 +5259,17 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B68" s="5">
-        <v>46224.69195275463</v>
+        <v>46224.69183667824</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46224.88781885417</v>
+        <v>46224.8876578125</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>218</v>
+        <v>145</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5218,10 +5281,10 @@
         <v>52</v>
       </c>
       <c r="I68" s="5">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="J68" s="5">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>26</v>
@@ -5233,43 +5296,33 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q68" s="5">
-        <v>46286</v>
-      </c>
-      <c r="R68" s="5">
-        <v>46286</v>
-      </c>
-      <c r="S68" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T68" s="6">
-        <v>0</v>
-      </c>
-      <c r="U68" s="12" t="s">
-        <v>67</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Q68" s="6"/>
+      <c r="R68" s="6"/>
+      <c r="S68" s="6"/>
+      <c r="T68" s="6"/>
+      <c r="U68" s="6"/>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B69" s="9">
-        <v>46224.69195878472</v>
+        <v>46224.69195275463</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46224.888011284726</v>
+        <v>46232.62438170139</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>144</v>
+        <v>224</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5296,33 +5349,43 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q69" s="10"/>
-      <c r="R69" s="10"/>
-      <c r="S69" s="10"/>
-      <c r="T69" s="10"/>
-      <c r="U69" s="10"/>
+        <v>226</v>
+      </c>
+      <c r="Q69" s="9">
+        <v>46286</v>
+      </c>
+      <c r="R69" s="9">
+        <v>46286</v>
+      </c>
+      <c r="S69" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T69" s="10">
+        <v>0</v>
+      </c>
+      <c r="U69" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B70" s="5">
-        <v>46224.69196560185</v>
+        <v>46224.69195878472</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46224.88800827546</v>
+        <v>46224.888011284726</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5349,13 +5412,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5365,17 +5428,17 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B71" s="9">
-        <v>46224.69197195602</v>
+        <v>46224.69196560185</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46224.888004699074</v>
+        <v>46224.88800827546</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5402,13 +5465,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5418,17 +5481,17 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B72" s="5">
-        <v>46224.6920590625</v>
+        <v>46224.69197195602</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46224.88781516204</v>
+        <v>46224.888004699074</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>227</v>
+        <v>145</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5440,10 +5503,10 @@
         <v>52</v>
       </c>
       <c r="I72" s="5">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="J72" s="5">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>26</v>
@@ -5455,43 +5518,33 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>142</v>
+        <v>233</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q72" s="5">
-        <v>46287</v>
-      </c>
-      <c r="R72" s="5">
-        <v>46287</v>
-      </c>
-      <c r="S72" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T72" s="6">
-        <v>0</v>
-      </c>
-      <c r="U72" s="12" t="s">
-        <v>67</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="Q72" s="6"/>
+      <c r="R72" s="6"/>
+      <c r="S72" s="6"/>
+      <c r="T72" s="6"/>
+      <c r="U72" s="6"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B73" s="9">
-        <v>46224.69206486111</v>
+        <v>46224.6920590625</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46224.888117256945</v>
+        <v>46232.62438170139</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>144</v>
+        <v>235</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5518,33 +5571,43 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q73" s="10"/>
-      <c r="R73" s="10"/>
-      <c r="S73" s="10"/>
-      <c r="T73" s="10"/>
-      <c r="U73" s="10"/>
+        <v>237</v>
+      </c>
+      <c r="Q73" s="9">
+        <v>46287</v>
+      </c>
+      <c r="R73" s="9">
+        <v>46287</v>
+      </c>
+      <c r="S73" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T73" s="10">
+        <v>0</v>
+      </c>
+      <c r="U73" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B74" s="5">
-        <v>46224.69207089121</v>
+        <v>46224.69206486111</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46224.88811447917</v>
+        <v>46224.888117256945</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5571,13 +5634,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5587,17 +5650,17 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B75" s="9">
-        <v>46224.69207630787</v>
+        <v>46224.69207089121</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46224.88811143518</v>
+        <v>46224.88811447917</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5624,13 +5687,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5640,17 +5703,17 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B76" s="5">
-        <v>46224.692210925925</v>
+        <v>46224.69207630787</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46224.88781181713</v>
+        <v>46224.88811143518</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5662,10 +5725,10 @@
         <v>52</v>
       </c>
       <c r="I76" s="5">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="J76" s="5">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>26</v>
@@ -5677,43 +5740,33 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>142</v>
+        <v>239</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q76" s="5">
-        <v>46288</v>
-      </c>
-      <c r="R76" s="5">
-        <v>46288</v>
-      </c>
-      <c r="S76" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T76" s="6">
-        <v>0</v>
-      </c>
-      <c r="U76" s="12" t="s">
-        <v>67</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="Q76" s="6"/>
+      <c r="R76" s="6"/>
+      <c r="S76" s="6"/>
+      <c r="T76" s="6"/>
+      <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B77" s="9">
-        <v>46224.69221851852</v>
+        <v>46224.692210925925</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46224.88822145833</v>
+        <v>46232.62438108797</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5740,33 +5793,43 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q77" s="10"/>
-      <c r="R77" s="10"/>
-      <c r="S77" s="10"/>
-      <c r="T77" s="10"/>
-      <c r="U77" s="10"/>
+        <v>246</v>
+      </c>
+      <c r="Q77" s="9">
+        <v>46288</v>
+      </c>
+      <c r="R77" s="9">
+        <v>46288</v>
+      </c>
+      <c r="S77" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T77" s="10">
+        <v>0</v>
+      </c>
+      <c r="U77" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B78" s="5">
-        <v>46224.692225335646</v>
+        <v>46224.69221851852</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46224.88821883102</v>
+        <v>46224.88822145833</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5793,13 +5856,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5809,17 +5872,17 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B79" s="9">
-        <v>46224.69223655092</v>
+        <v>46224.692225335646</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46224.88821421296</v>
+        <v>46224.88821883102</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -5846,13 +5909,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -5862,17 +5925,17 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B80" s="5">
-        <v>46224.69235351852</v>
+        <v>46224.69223655092</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46224.887808576386</v>
+        <v>46224.88821421296</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>244</v>
+        <v>145</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -5884,10 +5947,10 @@
         <v>52</v>
       </c>
       <c r="I80" s="5">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="J80" s="5">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
@@ -5899,43 +5962,33 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>142</v>
+        <v>253</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q80" s="5">
-        <v>46289</v>
-      </c>
-      <c r="R80" s="5">
-        <v>46289</v>
-      </c>
-      <c r="S80" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T80" s="6">
-        <v>0</v>
-      </c>
-      <c r="U80" s="12" t="s">
-        <v>67</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="Q80" s="6"/>
+      <c r="R80" s="6"/>
+      <c r="S80" s="6"/>
+      <c r="T80" s="6"/>
+      <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B81" s="9">
-        <v>46224.6923596875</v>
+        <v>46224.69235351852</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46224.88831505787</v>
+        <v>46232.62438291666</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>144</v>
+        <v>214</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -5947,48 +6000,58 @@
         <v>52</v>
       </c>
       <c r="I81" s="9">
+        <v>46290</v>
+      </c>
+      <c r="J81" s="9">
+        <v>46290</v>
+      </c>
+      <c r="K81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N81" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="O81" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="P81" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q81" s="9">
         <v>46289</v>
       </c>
-      <c r="J81" s="9">
+      <c r="R81" s="9">
         <v>46289</v>
       </c>
-      <c r="K81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="O81" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="P81" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q81" s="10"/>
-      <c r="R81" s="10"/>
-      <c r="S81" s="10"/>
-      <c r="T81" s="10"/>
-      <c r="U81" s="10"/>
+      <c r="S81" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T81" s="10">
+        <v>0</v>
+      </c>
+      <c r="U81" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B82" s="5">
-        <v>46224.69236840278</v>
+        <v>46224.6923596875</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46224.88831152778</v>
+        <v>46224.88831505787</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6015,13 +6078,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6031,17 +6094,17 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="B83" s="9">
-        <v>46224.69237796296</v>
+        <v>46224.69236840278</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46224.88830864584</v>
+        <v>46224.88831152778</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6068,13 +6131,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6084,17 +6147,17 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="B84" s="5">
-        <v>46224.69253115741</v>
+        <v>46224.69237796296</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46224.88780266204</v>
+        <v>46224.88830864584</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>250</v>
+        <v>145</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6106,10 +6169,10 @@
         <v>52</v>
       </c>
       <c r="I84" s="5">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="J84" s="5">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>26</v>
@@ -6121,43 +6184,33 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q84" s="5">
-        <v>46293</v>
-      </c>
-      <c r="R84" s="5">
-        <v>46293</v>
-      </c>
-      <c r="S84" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T84" s="6">
-        <v>0</v>
-      </c>
-      <c r="U84" s="12" t="s">
-        <v>67</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="Q84" s="6"/>
+      <c r="R84" s="6"/>
+      <c r="S84" s="6"/>
+      <c r="T84" s="6"/>
+      <c r="U84" s="6"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="B85" s="9">
-        <v>46224.69253806713</v>
+        <v>46224.69253115741</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46224.88840122685</v>
+        <v>46232.62438199074</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>144</v>
+        <v>256</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6168,7 +6221,9 @@
       <c r="H85" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I85" s="10"/>
+      <c r="I85" s="9">
+        <v>46293</v>
+      </c>
       <c r="J85" s="9">
         <v>46293</v>
       </c>
@@ -6182,33 +6237,43 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>144</v>
+        <v>262</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q85" s="10"/>
-      <c r="R85" s="10"/>
-      <c r="S85" s="10"/>
-      <c r="T85" s="10"/>
-      <c r="U85" s="10"/>
+        <v>263</v>
+      </c>
+      <c r="Q85" s="9">
+        <v>46293</v>
+      </c>
+      <c r="R85" s="9">
+        <v>46293</v>
+      </c>
+      <c r="S85" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T85" s="10">
+        <v>0</v>
+      </c>
+      <c r="U85" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="B86" s="5">
-        <v>46224.69254259259</v>
+        <v>46224.69253806713</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46224.88839846065</v>
+        <v>46224.88840122685</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6233,13 +6298,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6249,17 +6314,17 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="B87" s="9">
-        <v>46224.69254695602</v>
+        <v>46224.69254259259</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46224.888395601854</v>
+        <v>46224.88839846065</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6284,13 +6349,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6300,27 +6365,31 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="B88" s="5">
-        <v>46224.69261697917</v>
+        <v>46224.69254695602</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46224.88265856481</v>
+        <v>46224.888395601854</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>257</v>
+        <v>145</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
+        <v>51</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
+      <c r="J88" s="5">
+        <v>46293</v>
+      </c>
       <c r="K88" s="6" t="s">
         <v>26</v>
       </c>
@@ -6328,16 +6397,16 @@
         <v>26</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>26</v>
+        <v>256</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>258</v>
+        <v>145</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>26</v>
+        <v>265</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6347,33 +6416,27 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="B89" s="9">
-        <v>46224.69265170139</v>
+        <v>46224.69261697917</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46224.888549525465</v>
+        <v>46224.88265856481</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="I89" s="9">
-        <v>46294</v>
-      </c>
-      <c r="J89" s="9">
-        <v>46294</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H89" s="10"/>
+      <c r="I89" s="10"/>
+      <c r="J89" s="10"/>
       <c r="K89" s="10" t="s">
         <v>26</v>
       </c>
@@ -6381,55 +6444,45 @@
         <v>26</v>
       </c>
       <c r="M89" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>257</v>
+        <v>26</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q89" s="9">
-        <v>46294</v>
-      </c>
-      <c r="R89" s="9">
-        <v>46294</v>
-      </c>
-      <c r="S89" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T89" s="10">
-        <v>0</v>
-      </c>
-      <c r="U89" s="12" t="s">
-        <v>67</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q89" s="10"/>
+      <c r="R89" s="10"/>
+      <c r="S89" s="10"/>
+      <c r="T89" s="10"/>
+      <c r="U89" s="10"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B90" s="5">
-        <v>46224.69265774306</v>
+        <v>46224.69265170139</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46224.88851116898</v>
+        <v>46224.888549525465</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>144</v>
+        <v>263</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="I90" s="5">
         <v>46294</v>
@@ -6447,42 +6500,52 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>144</v>
+        <v>256</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="6"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
+        <v>274</v>
+      </c>
+      <c r="Q90" s="5">
+        <v>46294</v>
+      </c>
+      <c r="R90" s="5">
+        <v>46294</v>
+      </c>
+      <c r="S90" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T90" s="6">
+        <v>0</v>
+      </c>
+      <c r="U90" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="B91" s="9">
-        <v>46224.69266123843</v>
+        <v>46224.69265774306</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46224.8885084838</v>
+        <v>46224.88851116898</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="I91" s="9">
         <v>46294</v>
@@ -6500,13 +6563,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6516,26 +6579,26 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="B92" s="5">
-        <v>46224.692664456015</v>
+        <v>46224.69266123843</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46224.88850347222</v>
+        <v>46224.8885084838</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="I92" s="5">
         <v>46294</v>
@@ -6553,13 +6616,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6569,32 +6632,32 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B93" s="9">
-        <v>46224.69271221065</v>
+        <v>46224.692664456015</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46224.88867554398</v>
+        <v>46224.88850347222</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>51</v>
+        <v>272</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>52</v>
+        <v>273</v>
       </c>
       <c r="I93" s="9">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="J93" s="9">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="K93" s="10" t="s">
         <v>26</v>
@@ -6606,43 +6669,33 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>260</v>
+        <v>145</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q93" s="9">
-        <v>46295</v>
-      </c>
-      <c r="R93" s="9">
-        <v>46295</v>
-      </c>
-      <c r="S93" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T93" s="10">
-        <v>0</v>
-      </c>
-      <c r="U93" s="12" t="s">
-        <v>67</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="Q93" s="10"/>
+      <c r="R93" s="10"/>
+      <c r="S93" s="10"/>
+      <c r="T93" s="10"/>
+      <c r="U93" s="10"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B94" s="5">
-        <v>46224.69271712963</v>
+        <v>46224.69271221065</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46224.888643495375</v>
+        <v>46224.88867554398</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>144</v>
+        <v>279</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6653,7 +6706,9 @@
       <c r="H94" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I94" s="6"/>
+      <c r="I94" s="5">
+        <v>46295</v>
+      </c>
       <c r="J94" s="5">
         <v>46295</v>
       </c>
@@ -6667,33 +6722,43 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>144</v>
+        <v>263</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6"/>
-      <c r="S94" s="6"/>
-      <c r="T94" s="6"/>
-      <c r="U94" s="6"/>
+        <v>280</v>
+      </c>
+      <c r="Q94" s="5">
+        <v>46295</v>
+      </c>
+      <c r="R94" s="5">
+        <v>46295</v>
+      </c>
+      <c r="S94" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T94" s="6">
+        <v>0</v>
+      </c>
+      <c r="U94" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B95" s="9">
-        <v>46224.692723113425</v>
+        <v>46224.69271712963</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46224.88864100694</v>
+        <v>46224.888643495375</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6718,13 +6783,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6734,17 +6799,17 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B96" s="5">
-        <v>46224.692728483795</v>
+        <v>46224.692723113425</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46224.88863769676</v>
+        <v>46224.88864100694</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6769,13 +6834,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6785,32 +6850,30 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B97" s="9">
-        <v>46224.692771875</v>
+        <v>46224.692728483795</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46224.88885393519</v>
+        <v>46224.88863769676</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>274</v>
+        <v>145</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>176</v>
+        <v>51</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="I97" s="9">
-        <v>46296</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="I97" s="10"/>
       <c r="J97" s="9">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="K97" s="10" t="s">
         <v>26</v>
@@ -6822,52 +6885,42 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q97" s="9">
-        <v>46296</v>
-      </c>
-      <c r="R97" s="9">
-        <v>46296</v>
-      </c>
-      <c r="S97" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T97" s="10">
-        <v>0</v>
-      </c>
-      <c r="U97" s="12" t="s">
-        <v>67</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="Q97" s="10"/>
+      <c r="R97" s="10"/>
+      <c r="S97" s="10"/>
+      <c r="T97" s="10"/>
+      <c r="U97" s="10"/>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B98" s="5">
-        <v>46224.69280849537</v>
+        <v>46224.692771875</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46224.88880863426</v>
+        <v>46224.88885393519</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>144</v>
+        <v>285</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I98" s="5">
         <v>46296</v>
@@ -6885,42 +6938,52 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>144</v>
+        <v>279</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q98" s="6"/>
-      <c r="R98" s="6"/>
-      <c r="S98" s="6"/>
-      <c r="T98" s="6"/>
-      <c r="U98" s="6"/>
+        <v>286</v>
+      </c>
+      <c r="Q98" s="5">
+        <v>46296</v>
+      </c>
+      <c r="R98" s="5">
+        <v>46296</v>
+      </c>
+      <c r="S98" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T98" s="6">
+        <v>0</v>
+      </c>
+      <c r="U98" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="B99" s="9">
-        <v>46224.69281277778</v>
+        <v>46224.69280849537</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46224.888805462964</v>
+        <v>46224.88880863426</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I99" s="9">
         <v>46296</v>
@@ -6938,13 +7001,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -6954,26 +7017,26 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="B100" s="5">
-        <v>46224.69281645834</v>
+        <v>46224.69281277778</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46224.88880255787</v>
+        <v>46224.888805462964</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I100" s="5">
         <v>46296</v>
@@ -6991,13 +7054,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7007,32 +7070,32 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B101" s="9">
-        <v>46224.692877442125</v>
+        <v>46224.69281645834</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46224.88918993056</v>
+        <v>46224.88880255787</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>280</v>
+        <v>145</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I101" s="9">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="J101" s="9">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="K101" s="10" t="s">
         <v>26</v>
@@ -7044,52 +7107,42 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>274</v>
+        <v>145</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q101" s="9">
-        <v>46297</v>
-      </c>
-      <c r="R101" s="9">
-        <v>46297</v>
-      </c>
-      <c r="S101" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T101" s="10">
-        <v>0</v>
-      </c>
-      <c r="U101" s="12" t="s">
-        <v>67</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="Q101" s="10"/>
+      <c r="R101" s="10"/>
+      <c r="S101" s="10"/>
+      <c r="T101" s="10"/>
+      <c r="U101" s="10"/>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B102" s="5">
-        <v>46224.69288434028</v>
+        <v>46224.692877442125</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46224.88913273148</v>
+        <v>46224.88918993056</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>144</v>
+        <v>291</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I102" s="5">
         <v>46297</v>
@@ -7107,42 +7160,52 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>144</v>
+        <v>285</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="6"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
+        <v>292</v>
+      </c>
+      <c r="Q102" s="5">
+        <v>46297</v>
+      </c>
+      <c r="R102" s="5">
+        <v>46297</v>
+      </c>
+      <c r="S102" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0</v>
+      </c>
+      <c r="U102" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B103" s="9">
-        <v>46224.69288743056</v>
+        <v>46224.69288434028</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46224.8891297338</v>
+        <v>46224.88913273148</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I103" s="9">
         <v>46297</v>
@@ -7160,13 +7223,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7176,26 +7239,26 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B104" s="5">
-        <v>46224.692890509265</v>
+        <v>46224.69288743056</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46224.88912665509</v>
+        <v>46224.8891297338</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I104" s="5">
         <v>46297</v>
@@ -7213,13 +7276,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7229,27 +7292,33 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B105" s="9">
-        <v>46224.692977743056</v>
+        <v>46224.692890509265</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46224.88292137731</v>
+        <v>46224.88912665509</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>287</v>
+        <v>145</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H105" s="10"/>
-      <c r="I105" s="10"/>
-      <c r="J105" s="10"/>
+        <v>177</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="I105" s="9">
+        <v>46297</v>
+      </c>
+      <c r="J105" s="9">
+        <v>46297</v>
+      </c>
       <c r="K105" s="10" t="s">
         <v>26</v>
       </c>
@@ -7257,16 +7326,16 @@
         <v>26</v>
       </c>
       <c r="M105" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>26</v>
+        <v>291</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>288</v>
+        <v>145</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>26</v>
+        <v>294</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7276,33 +7345,27 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B106" s="5">
-        <v>46224.69298071759</v>
+        <v>46224.692977743056</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46224.88926996528</v>
+        <v>46224.88292137731</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="I106" s="5">
-        <v>46300</v>
-      </c>
-      <c r="J106" s="5">
-        <v>46304</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H106" s="6"/>
+      <c r="I106" s="6"/>
+      <c r="J106" s="6"/>
       <c r="K106" s="6" t="s">
         <v>26</v>
       </c>
@@ -7310,55 +7373,45 @@
         <v>26</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>287</v>
+        <v>26</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q106" s="5">
-        <v>46304</v>
-      </c>
-      <c r="R106" s="5">
-        <v>46300</v>
-      </c>
-      <c r="S106" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T106" s="6">
-        <v>0</v>
-      </c>
-      <c r="U106" s="12" t="s">
-        <v>67</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q106" s="6"/>
+      <c r="R106" s="6"/>
+      <c r="S106" s="6"/>
+      <c r="T106" s="6"/>
+      <c r="U106" s="6"/>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B107" s="9">
-        <v>46224.693000983796</v>
+        <v>46224.69298071759</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46224.88933664352</v>
+        <v>46224.88926996528</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>30</v>
+        <v>302</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>31</v>
+        <v>303</v>
       </c>
       <c r="I107" s="9">
         <v>46300</v>
@@ -7376,13 +7429,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="Q107" s="9">
         <v>46304</v>
@@ -7396,8 +7449,71 @@
       <c r="T107" s="10">
         <v>0</v>
       </c>
-      <c r="U107" s="12" t="s">
-        <v>67</v>
+      <c r="U107" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B108" s="5">
+        <v>46224.693000983796</v>
+      </c>
+      <c r="C108" s="6"/>
+      <c r="D108" s="5">
+        <v>46224.88933664352</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I108" s="5">
+        <v>46300</v>
+      </c>
+      <c r="J108" s="5">
+        <v>46304</v>
+      </c>
+      <c r="K108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N108" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="O108" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="P108" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q108" s="5">
+        <v>46304</v>
+      </c>
+      <c r="R108" s="5">
+        <v>46300</v>
+      </c>
+      <c r="S108" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T108" s="6">
+        <v>0</v>
+      </c>
+      <c r="U108" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -3442,7 +3442,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46232.57441020833</v>
+        <v>46234.185530567134</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>133</v>
@@ -3486,8 +3486,8 @@
       <c r="R36" s="5">
         <v>46206</v>
       </c>
-      <c r="S36" s="7" t="s">
-        <v>32</v>
+      <c r="S36" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -428,16 +428,16 @@
     <t>Ingenieria y diseñoo:,Plano Definitivos OT 4375</t>
   </si>
   <si>
+    <t>1216762846409976</t>
+  </si>
+  <si>
+    <t>Plano Definitivos OT 4375</t>
+  </si>
+  <si>
+    <t>Check Planos OT 4375,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216762846409976</t>
-  </si>
-  <si>
-    <t>Plano Definitivos OT 4375</t>
-  </si>
-  <si>
-    <t>Check Planos OT 4375,Ingenieria y diseñoo:</t>
   </si>
   <si>
     <t>1216762846410001</t>
@@ -3379,7 +3379,7 @@
         <v>46232.574391863425</v>
       </c>
       <c r="D35" s="9">
-        <v>46232.57441003472</v>
+        <v>46235.195113483795</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>127</v>
@@ -3423,8 +3423,8 @@
       <c r="R35" s="9">
         <v>46230</v>
       </c>
-      <c r="S35" s="12" t="s">
-        <v>131</v>
+      <c r="S35" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -3435,7 +3435,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46224.69120917824</v>
@@ -3445,7 +3445,7 @@
         <v>46234.185530567134</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3478,7 +3478,7 @@
         <v>127</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q36" s="5">
         <v>46241</v>
@@ -3487,7 +3487,7 @@
         <v>46206</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -3538,7 +3538,7 @@
         <v>124</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>138</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -236,6 +236,9 @@
     <t>Generación OC corte laser  OT 4375,Propuesta compras:</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
@@ -435,9 +438,6 @@
   </si>
   <si>
     <t>Check Planos OT 4375,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1216762846410001</t>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46238.48599590278</v>
+        <v>46239.19517064815</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>63</v>
@@ -2346,29 +2346,29 @@
       <c r="R16" s="5">
         <v>46245</v>
       </c>
-      <c r="S16" s="7" t="s">
-        <v>32</v>
+      <c r="S16" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="T16" s="6">
         <v>0</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" s="9">
         <v>46224.691050636575</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46238.48599563657</v>
+        <v>46239.19517074074</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2401,7 +2401,7 @@
         <v>65</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q17" s="9">
         <v>46246</v>
@@ -2409,29 +2409,29 @@
       <c r="R17" s="9">
         <v>46245</v>
       </c>
-      <c r="S17" s="7" t="s">
-        <v>32</v>
+      <c r="S17" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B18" s="5">
         <v>46224.691053912036</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46238.48599585648</v>
+        <v>46239.1951708912</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2464,7 +2464,7 @@
         <v>65</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q18" s="5">
         <v>46246</v>
@@ -2472,29 +2472,29 @@
       <c r="R18" s="5">
         <v>46245</v>
       </c>
-      <c r="S18" s="7" t="s">
-        <v>32</v>
+      <c r="S18" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B19" s="9">
         <v>46224.69105851852</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46238.48599581019</v>
+        <v>46239.195171238425</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2527,7 +2527,7 @@
         <v>65</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q19" s="9">
         <v>46246</v>
@@ -2535,19 +2535,19 @@
       <c r="R19" s="9">
         <v>46245</v>
       </c>
-      <c r="S19" s="7" t="s">
-        <v>32</v>
+      <c r="S19" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
       </c>
       <c r="U19" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B20" s="5">
         <v>46224.69093564815</v>
@@ -2557,7 +2557,7 @@
         <v>46224.72969400463</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2581,7 +2581,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2594,7 +2594,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" s="9">
         <v>46224.69110914352</v>
@@ -2604,16 +2604,16 @@
         <v>46224.88562534722</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I21" s="9">
         <v>46248</v>
@@ -2631,13 +2631,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q21" s="9">
         <v>46259</v>
@@ -2652,12 +2652,12 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" s="5">
         <v>46224.691113368055</v>
@@ -2667,16 +2667,16 @@
         <v>46224.88573403935</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I22" s="5">
         <v>46247</v>
@@ -2694,13 +2694,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
@@ -2711,12 +2711,12 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="9">
         <v>46224.69111763889</v>
@@ -2726,16 +2726,16 @@
         <v>46224.885731030095</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I23" s="9">
         <v>46251</v>
@@ -2753,13 +2753,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2770,12 +2770,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="5">
         <v>46224.691122118056</v>
@@ -2785,16 +2785,16 @@
         <v>46224.88562246528</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I24" s="5">
         <v>46248</v>
@@ -2812,10 +2812,10 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2833,12 +2833,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" s="9">
         <v>46224.69117694444</v>
@@ -2848,16 +2848,16 @@
         <v>46224.88583665509</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I25" s="9">
         <v>46247</v>
@@ -2875,13 +2875,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2891,7 +2891,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" s="5">
         <v>46224.691182546296</v>
@@ -2901,16 +2901,16 @@
         <v>46224.88583366898</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I26" s="5">
         <v>46251</v>
@@ -2928,13 +2928,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2944,7 +2944,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" s="9">
         <v>46224.69118782408</v>
@@ -2954,16 +2954,16 @@
         <v>46224.88561925926</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I27" s="9">
         <v>46248</v>
@@ -2981,10 +2981,10 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -3002,12 +3002,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B28" s="5">
         <v>46224.69119221065</v>
@@ -3017,16 +3017,16 @@
         <v>46224.88591563657</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -3044,13 +3044,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3060,7 +3060,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B29" s="9">
         <v>46224.69119738426</v>
@@ -3070,16 +3070,16 @@
         <v>46224.88591252315</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I29" s="9">
         <v>46251</v>
@@ -3097,13 +3097,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B30" s="5">
         <v>46224.72969201389</v>
@@ -3123,16 +3123,16 @@
         <v>46224.88605396991</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I30" s="5">
         <v>46260</v>
@@ -3150,10 +3150,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3171,12 +3171,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B31" s="9">
         <v>46224.72978952546</v>
@@ -3186,16 +3186,16 @@
         <v>46237.55371150463</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3213,13 +3213,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3229,7 +3229,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5">
         <v>46224.72983336805</v>
@@ -3239,16 +3239,16 @@
         <v>46224.886155405096</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I32" s="5">
         <v>46258</v>
@@ -3266,13 +3266,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B33" s="9">
         <v>46224.72985208333</v>
@@ -3292,16 +3292,16 @@
         <v>46224.88628099537</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I33" s="9">
         <v>46289</v>
@@ -3319,13 +3319,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3335,7 +3335,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46224.690940555556</v>
@@ -3345,7 +3345,7 @@
         <v>46238.48598052083</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>25</v>
@@ -3369,7 +3369,7 @@
         <v>26</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3382,7 +3382,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" s="9">
         <v>46224.6912024537</v>
@@ -3394,16 +3394,16 @@
         <v>46235.195113483795</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I35" s="9">
         <v>46230</v>
@@ -3421,13 +3421,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>43</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q35" s="9">
         <v>46234</v>
@@ -3447,7 +3447,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46224.69120917824</v>
@@ -3459,16 +3459,16 @@
         <v>46238.48594296296</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46237</v>
@@ -3486,13 +3486,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="5">
         <v>46241</v>
@@ -3501,7 +3501,7 @@
         <v>46206</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3551,10 +3551,10 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>138</v>
@@ -3566,7 +3566,7 @@
         <v>46244</v>
       </c>
       <c r="S37" s="12" t="s">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="T37" s="10">
         <v>1</v>
@@ -3614,13 +3614,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>143</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q38" s="5">
         <v>46290</v>
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="U38" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -3880,7 +3880,7 @@
         <v>151</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>157</v>
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -3943,7 +3943,7 @@
         <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>160</v>
@@ -3961,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4006,7 +4006,7 @@
         <v>151</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>163</v>
@@ -4024,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4045,10 +4045,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I46" s="5">
         <v>46261</v>
@@ -4087,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4108,10 +4108,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I47" s="9">
         <v>46261</v>
@@ -4150,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4171,10 +4171,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4275,7 +4275,7 @@
         <v>46224.88693119213</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4305,7 +4305,7 @@
         <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>179</v>
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4338,7 +4338,7 @@
         <v>46224.887193206014</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4428,7 +4428,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>182</v>
@@ -4481,7 +4481,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>185</v>
@@ -4534,7 +4534,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>188</v>
@@ -4608,7 +4608,7 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4877,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="U60" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5003,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5164,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5386,7 +5386,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5608,7 +5608,7 @@
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5830,7 +5830,7 @@
         <v>0</v>
       </c>
       <c r="U77" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6052,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6274,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="U85" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="U90" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
@@ -6759,7 +6759,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -6975,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -7197,7 +7197,7 @@
         <v>0</v>
       </c>
       <c r="U102" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
@@ -7466,7 +7466,7 @@
         <v>0</v>
       </c>
       <c r="U107" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
@@ -7529,7 +7529,7 @@
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="303">
   <si>
     <t>50001576- "XEMORTIZ FIRST MAJESTIC"</t>
   </si>
@@ -668,139 +668,127 @@
     <t>Montaje Rodete OT 4375,Montaje motor OT 4375,Montaje Alabe OT 4375,Revestimiento OT 4375</t>
   </si>
   <si>
-    <t>1216991344494299</t>
-  </si>
-  <si>
-    <t>Conexión eléctrica OT 4375</t>
+    <t>1216763090891690</t>
+  </si>
+  <si>
+    <t>Revestimiento OT 4375</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje Alabe OT 4375</t>
+  </si>
+  <si>
+    <t>1216762727729087</t>
+  </si>
+  <si>
+    <t>Revestimiento OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216762727729102</t>
+  </si>
+  <si>
+    <t>1216763050324049</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Revestimiento OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216762959232537</t>
+  </si>
+  <si>
+    <t>Montaje Alabe OT 4375</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Revestimiento OT 4375</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje Rodete OT 4375</t>
+  </si>
+  <si>
+    <t>1216763050389900</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Recepcion Alabe OT 4375,Check Planos OT 4375</t>
+  </si>
+  <si>
+    <t>Montaje Alabe OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216763159790599</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Montaje Alabe OT 4375</t>
+  </si>
+  <si>
+    <t>1216763159790624</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe OT 4375,Check Planos OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216762959307816</t>
+  </si>
+  <si>
+    <t>Montaje Rodete OT 4375</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Montaje Alabe OT 4375</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje motor OT 4375</t>
+  </si>
+  <si>
+    <t>1216762959307831</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>Montaje Rodete OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216763159826891</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Montaje Rodete OT 4375</t>
+  </si>
+  <si>
+    <t>1216763159826911</t>
+  </si>
+  <si>
+    <t>1216762959410712</t>
   </si>
   <si>
     <t>Montaje motor OT 4375</t>
   </si>
   <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Montaje Rodete OT 4375</t>
+  </si>
+  <si>
+    <t>1216762959410727</t>
+  </si>
+  <si>
+    <t>Recepcion motor OT 4375,Check Planos OT 4375</t>
+  </si>
+  <si>
+    <t>Montaje motor OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216762959411227</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Montaje motor OT 4375</t>
+  </si>
+  <si>
+    <t>1216762959411247</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Recepcion motor OT 4375</t>
+  </si>
+  <si>
+    <t>1216763091386830</t>
+  </si>
+  <si>
     <t>Pruebas FAT OT 4375</t>
-  </si>
-  <si>
-    <t>1216763090891690</t>
-  </si>
-  <si>
-    <t>Revestimiento OT 4375</t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje Alabe OT 4375</t>
-  </si>
-  <si>
-    <t>1216762727729087</t>
-  </si>
-  <si>
-    <t>Revestimiento OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216762727729102</t>
-  </si>
-  <si>
-    <t>1216763050324049</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Revestimiento OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216762959232537</t>
-  </si>
-  <si>
-    <t>Montaje Alabe OT 4375</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Revestimiento OT 4375</t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje Rodete OT 4375</t>
-  </si>
-  <si>
-    <t>1216763050389900</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Recepcion Alabe OT 4375,Check Planos OT 4375</t>
-  </si>
-  <si>
-    <t>Montaje Alabe OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216763159790599</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Montaje Alabe OT 4375</t>
-  </si>
-  <si>
-    <t>1216763159790624</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe OT 4375,Check Planos OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216762959307816</t>
-  </si>
-  <si>
-    <t>Montaje Rodete OT 4375</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Montaje Alabe OT 4375</t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje motor OT 4375</t>
-  </si>
-  <si>
-    <t>1216762959307831</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>Montaje Rodete OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216763159826891</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Montaje Rodete OT 4375</t>
-  </si>
-  <si>
-    <t>1216763159826911</t>
-  </si>
-  <si>
-    <t>1216762959410712</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Montaje Rodete OT 4375</t>
-  </si>
-  <si>
-    <t>Montaje:,Conexión eléctrica OT 4375</t>
-  </si>
-  <si>
-    <t>1216762959410727</t>
-  </si>
-  <si>
-    <t>Recepcion motor OT 4375,Check Planos OT 4375</t>
-  </si>
-  <si>
-    <t>Montaje motor OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216762959411227</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Montaje motor OT 4375</t>
-  </si>
-  <si>
-    <t>1216762959411247</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Recepcion motor OT 4375</t>
-  </si>
-  <si>
-    <t>1216763091386830</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Conexión eléctrica OT 4375</t>
   </si>
   <si>
     <t>RE-PINTADO OT 4375</t>
@@ -1477,7 +1465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U108"/>
+  <dimension ref="A1:U107"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -5058,11 +5046,11 @@
         <v>211</v>
       </c>
       <c r="B64" s="5">
-        <v>46232.603311631945</v>
+        <v>46224.69182049768</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46232.62438241898</v>
+        <v>46232.624381828704</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>212</v>
@@ -5071,14 +5059,16 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="6"/>
+        <v>51</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="I64" s="5">
-        <v>46289</v>
+        <v>46275</v>
       </c>
       <c r="J64" s="5">
-        <v>46289</v>
+        <v>46281</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>26</v>
@@ -5093,30 +5083,40 @@
         <v>209</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="P64" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="6"/>
-      <c r="S64" s="6"/>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
+      <c r="Q64" s="5">
+        <v>46281</v>
+      </c>
+      <c r="R64" s="5">
+        <v>46275</v>
+      </c>
+      <c r="S64" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T64" s="6">
+        <v>0</v>
+      </c>
+      <c r="U64" s="11" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B65" s="9">
-        <v>46224.69182049768</v>
+        <v>46224.691826967595</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46232.624381828704</v>
+        <v>46224.887663622685</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>216</v>
+        <v>145</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5143,40 +5143,30 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q65" s="9">
-        <v>46281</v>
-      </c>
-      <c r="R65" s="9">
-        <v>46275</v>
-      </c>
-      <c r="S65" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T65" s="10">
-        <v>0</v>
-      </c>
-      <c r="U65" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="10"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B66" s="5">
-        <v>46224.691826967595</v>
+        <v>46224.691831840275</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46224.887663622685</v>
+        <v>46224.8876609375</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>145</v>
@@ -5206,13 +5196,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>145</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5222,14 +5212,14 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B67" s="9">
-        <v>46224.691831840275</v>
+        <v>46224.69183667824</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46224.8876609375</v>
+        <v>46224.8876578125</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>145</v>
@@ -5259,13 +5249,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>145</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5275,17 +5265,17 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B68" s="5">
-        <v>46224.69183667824</v>
+        <v>46224.69195275463</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46224.8876578125</v>
+        <v>46232.62438170139</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5297,10 +5287,10 @@
         <v>52</v>
       </c>
       <c r="I68" s="5">
-        <v>46275</v>
+        <v>46286</v>
       </c>
       <c r="J68" s="5">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>26</v>
@@ -5312,33 +5302,43 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>145</v>
+        <v>221</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="Q68" s="6"/>
-      <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
-      <c r="T68" s="6"/>
-      <c r="U68" s="6"/>
+      <c r="Q68" s="5">
+        <v>46286</v>
+      </c>
+      <c r="R68" s="5">
+        <v>46286</v>
+      </c>
+      <c r="S68" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T68" s="6">
+        <v>0</v>
+      </c>
+      <c r="U68" s="11" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
         <v>223</v>
       </c>
       <c r="B69" s="9">
-        <v>46224.69195275463</v>
+        <v>46224.69195878472</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46232.62438170139</v>
+        <v>46238.48598511574</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>224</v>
+        <v>145</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5365,40 +5365,30 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="P69" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q69" s="9">
-        <v>46286</v>
-      </c>
-      <c r="R69" s="9">
-        <v>46286</v>
-      </c>
-      <c r="S69" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T69" s="10">
-        <v>0</v>
-      </c>
-      <c r="U69" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
+      <c r="S69" s="10"/>
+      <c r="T69" s="10"/>
+      <c r="U69" s="10"/>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B70" s="5">
-        <v>46224.69195878472</v>
+        <v>46224.69196560185</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46238.48598511574</v>
+        <v>46238.48598628472</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>145</v>
@@ -5428,13 +5418,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="O70" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="O70" s="6" t="s">
-        <v>228</v>
-      </c>
       <c r="P70" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5444,14 +5434,14 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B71" s="9">
-        <v>46224.69196560185</v>
+        <v>46224.69197195602</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46238.48598628472</v>
+        <v>46238.485982094906</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>145</v>
@@ -5481,13 +5471,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5497,17 +5487,17 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B72" s="5">
-        <v>46224.69197195602</v>
+        <v>46224.6920590625</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46238.485982094906</v>
+        <v>46232.62438170139</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>145</v>
+        <v>231</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5519,10 +5509,10 @@
         <v>52</v>
       </c>
       <c r="I72" s="5">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="J72" s="5">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>26</v>
@@ -5534,33 +5524,43 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="P72" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="6"/>
-      <c r="S72" s="6"/>
-      <c r="T72" s="6"/>
-      <c r="U72" s="6"/>
+      <c r="Q72" s="5">
+        <v>46287</v>
+      </c>
+      <c r="R72" s="5">
+        <v>46287</v>
+      </c>
+      <c r="S72" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T72" s="6">
+        <v>0</v>
+      </c>
+      <c r="U72" s="11" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
         <v>234</v>
       </c>
       <c r="B73" s="9">
-        <v>46224.6920590625</v>
+        <v>46224.69206486111</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46232.62438170139</v>
+        <v>46224.888117256945</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5587,40 +5587,30 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="O73" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="P73" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="P73" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q73" s="9">
-        <v>46287</v>
-      </c>
-      <c r="R73" s="9">
-        <v>46287</v>
-      </c>
-      <c r="S73" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T73" s="10">
-        <v>0</v>
-      </c>
-      <c r="U73" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="10"/>
+      <c r="U73" s="10"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B74" s="5">
-        <v>46224.69206486111</v>
+        <v>46224.69207089121</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46224.888117256945</v>
+        <v>46224.88811447917</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>145</v>
@@ -5650,13 +5640,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="O74" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="O74" s="6" t="s">
-        <v>239</v>
-      </c>
       <c r="P74" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5666,14 +5656,14 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B75" s="9">
-        <v>46224.69207089121</v>
+        <v>46224.69207630787</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46224.88811447917</v>
+        <v>46224.88811143518</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>145</v>
@@ -5703,13 +5693,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="O75" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="O75" s="10" t="s">
-        <v>239</v>
-      </c>
       <c r="P75" s="10" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5719,17 +5709,17 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B76" s="5">
-        <v>46224.69207630787</v>
+        <v>46224.692210925925</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46224.88811143518</v>
+        <v>46240.822117592594</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>145</v>
+        <v>241</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5741,10 +5731,10 @@
         <v>52</v>
       </c>
       <c r="I76" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="J76" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>26</v>
@@ -5756,33 +5746,43 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="6"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
+        <v>209</v>
+      </c>
+      <c r="Q76" s="5">
+        <v>46288</v>
+      </c>
+      <c r="R76" s="5">
+        <v>46288</v>
+      </c>
+      <c r="S76" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0</v>
+      </c>
+      <c r="U76" s="11" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B77" s="9">
-        <v>46224.692210925925</v>
+        <v>46224.69221851852</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46232.62438108797</v>
+        <v>46238.48598354167</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>213</v>
+        <v>145</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5809,40 +5809,30 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="O77" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="P77" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="P77" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q77" s="9">
-        <v>46288</v>
-      </c>
-      <c r="R77" s="9">
-        <v>46288</v>
-      </c>
-      <c r="S77" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T77" s="10">
-        <v>0</v>
-      </c>
-      <c r="U77" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
+      <c r="S77" s="10"/>
+      <c r="T77" s="10"/>
+      <c r="U77" s="10"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B78" s="5">
-        <v>46224.69221851852</v>
+        <v>46224.692225335646</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46238.48598354167</v>
+        <v>46238.48598415509</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>145</v>
@@ -5872,13 +5862,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5888,14 +5878,14 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B79" s="9">
-        <v>46224.692225335646</v>
+        <v>46224.69223655092</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46238.48598415509</v>
+        <v>46224.88821421296</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>145</v>
@@ -5925,13 +5915,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -5941,17 +5931,17 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B80" s="5">
-        <v>46224.69223655092</v>
+        <v>46224.69235351852</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46224.88821421296</v>
+        <v>46240.822117662035</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>145</v>
+        <v>251</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -5963,10 +5953,10 @@
         <v>52</v>
       </c>
       <c r="I80" s="5">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="J80" s="5">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
@@ -5978,33 +5968,43 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>253</v>
+        <v>143</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="6"/>
-      <c r="S80" s="6"/>
-      <c r="T80" s="6"/>
-      <c r="U80" s="6"/>
+        <v>252</v>
+      </c>
+      <c r="Q80" s="5">
+        <v>46289</v>
+      </c>
+      <c r="R80" s="5">
+        <v>46289</v>
+      </c>
+      <c r="S80" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T80" s="6">
+        <v>0</v>
+      </c>
+      <c r="U80" s="11" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B81" s="9">
-        <v>46224.69235351852</v>
+        <v>46224.6923596875</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46232.62438291666</v>
+        <v>46224.88831505787</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>214</v>
+        <v>145</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6016,10 +6016,10 @@
         <v>52</v>
       </c>
       <c r="I81" s="9">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="J81" s="9">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="K81" s="10" t="s">
         <v>26</v>
@@ -6031,40 +6031,30 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>209</v>
+        <v>251</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>255</v>
+        <v>143</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q81" s="9">
-        <v>46289</v>
-      </c>
-      <c r="R81" s="9">
-        <v>46289</v>
-      </c>
-      <c r="S81" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T81" s="10">
-        <v>0</v>
-      </c>
-      <c r="U81" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
+      <c r="S81" s="10"/>
+      <c r="T81" s="10"/>
+      <c r="U81" s="10"/>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B82" s="5">
-        <v>46224.6923596875</v>
+        <v>46224.69236840278</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46224.88831505787</v>
+        <v>46224.88831152778</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>145</v>
@@ -6094,13 +6084,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>143</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6110,14 +6100,14 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B83" s="9">
-        <v>46224.69236840278</v>
+        <v>46224.69237796296</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46224.88831152778</v>
+        <v>46224.88830864584</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>145</v>
@@ -6147,13 +6137,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>143</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6163,17 +6153,17 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B84" s="5">
-        <v>46224.69237796296</v>
+        <v>46224.69253115741</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46224.88830864584</v>
+        <v>46232.62438199074</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6185,10 +6175,10 @@
         <v>52</v>
       </c>
       <c r="I84" s="5">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="J84" s="5">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>26</v>
@@ -6200,33 +6190,43 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>143</v>
+        <v>258</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q84" s="6"/>
-      <c r="R84" s="6"/>
-      <c r="S84" s="6"/>
-      <c r="T84" s="6"/>
-      <c r="U84" s="6"/>
+        <v>259</v>
+      </c>
+      <c r="Q84" s="5">
+        <v>46293</v>
+      </c>
+      <c r="R84" s="5">
+        <v>46293</v>
+      </c>
+      <c r="S84" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T84" s="6">
+        <v>0</v>
+      </c>
+      <c r="U84" s="11" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B85" s="9">
-        <v>46224.69253115741</v>
+        <v>46224.69253806713</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46232.62438199074</v>
+        <v>46224.88840122685</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>256</v>
+        <v>145</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6237,9 +6237,7 @@
       <c r="H85" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I85" s="9">
-        <v>46293</v>
-      </c>
+      <c r="I85" s="10"/>
       <c r="J85" s="9">
         <v>46293</v>
       </c>
@@ -6253,40 +6251,30 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>262</v>
+        <v>145</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q85" s="9">
-        <v>46293</v>
-      </c>
-      <c r="R85" s="9">
-        <v>46293</v>
-      </c>
-      <c r="S85" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T85" s="10">
-        <v>0</v>
-      </c>
-      <c r="U85" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="Q85" s="10"/>
+      <c r="R85" s="10"/>
+      <c r="S85" s="10"/>
+      <c r="T85" s="10"/>
+      <c r="U85" s="10"/>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B86" s="5">
-        <v>46224.69253806713</v>
+        <v>46224.69254259259</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46224.88840122685</v>
+        <v>46224.88839846065</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>145</v>
@@ -6314,13 +6302,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>145</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6330,14 +6318,14 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B87" s="9">
-        <v>46224.69254259259</v>
+        <v>46224.69254695602</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46224.88839846065</v>
+        <v>46224.888395601854</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>145</v>
@@ -6365,13 +6353,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>145</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6381,31 +6369,27 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B88" s="5">
-        <v>46224.69254695602</v>
+        <v>46224.69261697917</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46224.888395601854</v>
+        <v>46224.88265856481</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>145</v>
+        <v>265</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>52</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H88" s="6"/>
       <c r="I88" s="6"/>
-      <c r="J88" s="5">
-        <v>46293</v>
-      </c>
+      <c r="J88" s="6"/>
       <c r="K88" s="6" t="s">
         <v>26</v>
       </c>
@@ -6413,16 +6397,16 @@
         <v>26</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>256</v>
+        <v>26</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>145</v>
+        <v>266</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>265</v>
+        <v>26</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6432,27 +6416,33 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B89" s="9">
-        <v>46224.69261697917</v>
+        <v>46224.69265170139</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46224.88265856481</v>
+        <v>46224.888549525465</v>
       </c>
       <c r="E89" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="F89" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="10"/>
-      <c r="I89" s="10"/>
-      <c r="J89" s="10"/>
+      <c r="I89" s="9">
+        <v>46294</v>
+      </c>
+      <c r="J89" s="9">
+        <v>46294</v>
+      </c>
       <c r="K89" s="10" t="s">
         <v>26</v>
       </c>
@@ -6460,45 +6450,55 @@
         <v>26</v>
       </c>
       <c r="M89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N89" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="O89" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="P89" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q89" s="9">
+        <v>46294</v>
+      </c>
+      <c r="R89" s="9">
+        <v>46294</v>
+      </c>
+      <c r="S89" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T89" s="10">
         <v>0</v>
       </c>
-      <c r="N89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O89" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q89" s="10"/>
-      <c r="R89" s="10"/>
-      <c r="S89" s="10"/>
-      <c r="T89" s="10"/>
-      <c r="U89" s="10"/>
+      <c r="U89" s="11" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>271</v>
       </c>
       <c r="B90" s="5">
-        <v>46224.69265170139</v>
+        <v>46224.69265774306</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46224.888549525465</v>
+        <v>46224.88851116898</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>263</v>
+        <v>145</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I90" s="5">
         <v>46294</v>
@@ -6516,40 +6516,30 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>256</v>
+        <v>145</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q90" s="5">
-        <v>46294</v>
-      </c>
-      <c r="R90" s="5">
-        <v>46294</v>
-      </c>
-      <c r="S90" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T90" s="6">
-        <v>0</v>
-      </c>
-      <c r="U90" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="Q90" s="6"/>
+      <c r="R90" s="6"/>
+      <c r="S90" s="6"/>
+      <c r="T90" s="6"/>
+      <c r="U90" s="6"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B91" s="9">
-        <v>46224.69265774306</v>
+        <v>46224.69266123843</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46224.88851116898</v>
+        <v>46224.8885084838</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>145</v>
@@ -6558,10 +6548,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I91" s="9">
         <v>46294</v>
@@ -6579,7 +6569,7 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>145</v>
@@ -6595,14 +6585,14 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B92" s="5">
-        <v>46224.69266123843</v>
+        <v>46224.692664456015</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46224.8885084838</v>
+        <v>46224.88850347222</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>145</v>
@@ -6611,10 +6601,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I92" s="5">
         <v>46294</v>
@@ -6632,7 +6622,7 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>145</v>
@@ -6648,32 +6638,32 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B93" s="9">
-        <v>46224.692664456015</v>
+        <v>46224.69271221065</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46224.88850347222</v>
+        <v>46224.88867554398</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>145</v>
+        <v>275</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>272</v>
+        <v>51</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>273</v>
+        <v>52</v>
       </c>
       <c r="I93" s="9">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="J93" s="9">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="K93" s="10" t="s">
         <v>26</v>
@@ -6685,33 +6675,43 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>145</v>
+        <v>259</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q93" s="10"/>
-      <c r="R93" s="10"/>
-      <c r="S93" s="10"/>
-      <c r="T93" s="10"/>
-      <c r="U93" s="10"/>
+        <v>276</v>
+      </c>
+      <c r="Q93" s="9">
+        <v>46295</v>
+      </c>
+      <c r="R93" s="9">
+        <v>46295</v>
+      </c>
+      <c r="S93" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T93" s="10">
+        <v>0</v>
+      </c>
+      <c r="U93" s="11" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B94" s="5">
-        <v>46224.69271221065</v>
+        <v>46224.69271712963</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46224.88867554398</v>
+        <v>46224.888643495375</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>279</v>
+        <v>145</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6722,9 +6722,7 @@
       <c r="H94" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I94" s="5">
-        <v>46295</v>
-      </c>
+      <c r="I94" s="6"/>
       <c r="J94" s="5">
         <v>46295</v>
       </c>
@@ -6738,40 +6736,30 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>263</v>
+        <v>145</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q94" s="5">
-        <v>46295</v>
-      </c>
-      <c r="R94" s="5">
-        <v>46295</v>
-      </c>
-      <c r="S94" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T94" s="6">
-        <v>0</v>
-      </c>
-      <c r="U94" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="Q94" s="6"/>
+      <c r="R94" s="6"/>
+      <c r="S94" s="6"/>
+      <c r="T94" s="6"/>
+      <c r="U94" s="6"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B95" s="9">
-        <v>46224.69271712963</v>
+        <v>46224.692723113425</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46224.888643495375</v>
+        <v>46224.88864100694</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>145</v>
@@ -6799,7 +6787,7 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>145</v>
@@ -6815,14 +6803,14 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B96" s="5">
-        <v>46224.692723113425</v>
+        <v>46224.692728483795</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46224.88864100694</v>
+        <v>46224.88863769676</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>145</v>
@@ -6850,7 +6838,7 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>145</v>
@@ -6866,30 +6854,32 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B97" s="9">
-        <v>46224.692728483795</v>
+        <v>46224.692771875</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46224.88863769676</v>
+        <v>46224.88885393519</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>145</v>
+        <v>281</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>51</v>
+        <v>177</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="I97" s="10"/>
+        <v>178</v>
+      </c>
+      <c r="I97" s="9">
+        <v>46296</v>
+      </c>
       <c r="J97" s="9">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="K97" s="10" t="s">
         <v>26</v>
@@ -6901,33 +6891,43 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>145</v>
+        <v>275</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q97" s="10"/>
-      <c r="R97" s="10"/>
-      <c r="S97" s="10"/>
-      <c r="T97" s="10"/>
-      <c r="U97" s="10"/>
+        <v>282</v>
+      </c>
+      <c r="Q97" s="9">
+        <v>46296</v>
+      </c>
+      <c r="R97" s="9">
+        <v>46296</v>
+      </c>
+      <c r="S97" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T97" s="10">
+        <v>0</v>
+      </c>
+      <c r="U97" s="11" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B98" s="5">
-        <v>46224.692771875</v>
+        <v>46224.69280849537</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46224.88885393519</v>
+        <v>46224.88880863426</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>285</v>
+        <v>145</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -6954,40 +6954,30 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>279</v>
+        <v>145</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="Q98" s="5">
-        <v>46296</v>
-      </c>
-      <c r="R98" s="5">
-        <v>46296</v>
-      </c>
-      <c r="S98" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T98" s="6">
-        <v>0</v>
-      </c>
-      <c r="U98" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="Q98" s="6"/>
+      <c r="R98" s="6"/>
+      <c r="S98" s="6"/>
+      <c r="T98" s="6"/>
+      <c r="U98" s="6"/>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B99" s="9">
-        <v>46224.69280849537</v>
+        <v>46224.69281277778</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46224.88880863426</v>
+        <v>46224.888805462964</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>145</v>
@@ -7017,7 +7007,7 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O99" s="10" t="s">
         <v>145</v>
@@ -7033,14 +7023,14 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B100" s="5">
-        <v>46224.69281277778</v>
+        <v>46224.69281645834</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46224.888805462964</v>
+        <v>46224.88880255787</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>145</v>
@@ -7070,7 +7060,7 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>145</v>
@@ -7086,17 +7076,17 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B101" s="9">
-        <v>46224.69281645834</v>
+        <v>46224.692877442125</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46224.88880255787</v>
+        <v>46224.88918993056</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>145</v>
+        <v>287</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7108,10 +7098,10 @@
         <v>178</v>
       </c>
       <c r="I101" s="9">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="J101" s="9">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="K101" s="10" t="s">
         <v>26</v>
@@ -7123,33 +7113,43 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>145</v>
+        <v>281</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q101" s="10"/>
-      <c r="R101" s="10"/>
-      <c r="S101" s="10"/>
-      <c r="T101" s="10"/>
-      <c r="U101" s="10"/>
+        <v>288</v>
+      </c>
+      <c r="Q101" s="9">
+        <v>46297</v>
+      </c>
+      <c r="R101" s="9">
+        <v>46297</v>
+      </c>
+      <c r="S101" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T101" s="10">
+        <v>0</v>
+      </c>
+      <c r="U101" s="11" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B102" s="5">
-        <v>46224.692877442125</v>
+        <v>46224.69288434028</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46224.88918993056</v>
+        <v>46224.88913273148</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>291</v>
+        <v>145</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7176,40 +7176,30 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>285</v>
+        <v>145</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q102" s="5">
-        <v>46297</v>
-      </c>
-      <c r="R102" s="5">
-        <v>46297</v>
-      </c>
-      <c r="S102" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T102" s="6">
-        <v>0</v>
-      </c>
-      <c r="U102" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="Q102" s="6"/>
+      <c r="R102" s="6"/>
+      <c r="S102" s="6"/>
+      <c r="T102" s="6"/>
+      <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B103" s="9">
-        <v>46224.69288434028</v>
+        <v>46224.69288743056</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46224.88913273148</v>
+        <v>46224.8891297338</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>145</v>
@@ -7239,13 +7229,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>145</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7255,14 +7245,14 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B104" s="5">
-        <v>46224.69288743056</v>
+        <v>46224.692890509265</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46224.8891297338</v>
+        <v>46224.88912665509</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>145</v>
@@ -7292,13 +7282,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>145</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7308,33 +7298,27 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B105" s="9">
-        <v>46224.692890509265</v>
+        <v>46224.692977743056</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46224.88912665509</v>
+        <v>46224.88292137731</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>145</v>
+        <v>294</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="I105" s="9">
-        <v>46297</v>
-      </c>
-      <c r="J105" s="9">
-        <v>46297</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H105" s="10"/>
+      <c r="I105" s="10"/>
+      <c r="J105" s="10"/>
       <c r="K105" s="10" t="s">
         <v>26</v>
       </c>
@@ -7342,16 +7326,16 @@
         <v>26</v>
       </c>
       <c r="M105" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>291</v>
+        <v>26</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>145</v>
+        <v>295</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>294</v>
+        <v>26</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7361,27 +7345,33 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B106" s="5">
-        <v>46224.692977743056</v>
+        <v>46224.69298071759</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46224.88292137731</v>
+        <v>46224.88926996528</v>
       </c>
       <c r="E106" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G106" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="F106" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
-      <c r="J106" s="6"/>
+      <c r="H106" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="I106" s="5">
+        <v>46300</v>
+      </c>
+      <c r="J106" s="5">
+        <v>46304</v>
+      </c>
       <c r="K106" s="6" t="s">
         <v>26</v>
       </c>
@@ -7389,45 +7379,55 @@
         <v>26</v>
       </c>
       <c r="M106" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N106" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="O106" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="P106" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q106" s="5">
+        <v>46304</v>
+      </c>
+      <c r="R106" s="5">
+        <v>46300</v>
+      </c>
+      <c r="S106" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T106" s="6">
         <v>0</v>
       </c>
-      <c r="N106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O106" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="P106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q106" s="6"/>
-      <c r="R106" s="6"/>
-      <c r="S106" s="6"/>
-      <c r="T106" s="6"/>
-      <c r="U106" s="6"/>
+      <c r="U106" s="11" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B107" s="9">
-        <v>46224.69298071759</v>
+        <v>46224.693000983796</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46224.88926996528</v>
+        <v>46224.88933664352</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>302</v>
+        <v>30</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>303</v>
+        <v>31</v>
       </c>
       <c r="I107" s="9">
         <v>46300</v>
@@ -7445,13 +7445,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="Q107" s="9">
         <v>46304</v>
@@ -7466,69 +7466,6 @@
         <v>0</v>
       </c>
       <c r="U107" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A108" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B108" s="5">
-        <v>46224.693000983796</v>
-      </c>
-      <c r="C108" s="6"/>
-      <c r="D108" s="5">
-        <v>46224.88933664352</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I108" s="5">
-        <v>46300</v>
-      </c>
-      <c r="J108" s="5">
-        <v>46304</v>
-      </c>
-      <c r="K108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N108" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="O108" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q108" s="5">
-        <v>46304</v>
-      </c>
-      <c r="R108" s="5">
-        <v>46300</v>
-      </c>
-      <c r="S108" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T108" s="6">
-        <v>0</v>
-      </c>
-      <c r="U108" s="11" t="s">
         <v>85</v>
       </c>
     </row>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -3444,7 +3444,7 @@
         <v>46238.48592310185</v>
       </c>
       <c r="D36" s="5">
-        <v>46238.48594296296</v>
+        <v>46242.166817314814</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>133</v>
@@ -3488,8 +3488,8 @@
       <c r="R36" s="5">
         <v>46206</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>67</v>
+      <c r="S36" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="302">
   <si>
     <t>50001576- "XEMORTIZ FIRST MAJESTIC"</t>
   </si>
@@ -234,9 +234,6 @@
   </si>
   <si>
     <t>Generación OC corte laser  OT 4375,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>Tarea en curso</t>
@@ -2290,7 +2287,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46246.25088706019</v>
+        <v>46247.16958072917</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>63</v>
@@ -2334,29 +2331,29 @@
       <c r="R16" s="5">
         <v>46245</v>
       </c>
-      <c r="S16" s="12" t="s">
-        <v>67</v>
+      <c r="S16" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T16" s="6">
         <v>0</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B17" s="9">
         <v>46224.691050636575</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46246.25088936342</v>
+        <v>46247.169573946754</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2389,7 +2386,7 @@
         <v>65</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q17" s="9">
         <v>46246</v>
@@ -2397,29 +2394,29 @@
       <c r="R17" s="9">
         <v>46245</v>
       </c>
-      <c r="S17" s="12" t="s">
-        <v>67</v>
+      <c r="S17" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5">
         <v>46224.691053912036</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46246.250890497686</v>
+        <v>46247.169574178246</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2452,7 +2449,7 @@
         <v>65</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q18" s="5">
         <v>46246</v>
@@ -2460,29 +2457,29 @@
       <c r="R18" s="5">
         <v>46245</v>
       </c>
-      <c r="S18" s="12" t="s">
-        <v>67</v>
+      <c r="S18" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B19" s="9">
         <v>46224.69105851852</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46246.25088412037</v>
+        <v>46247.16957373843</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2515,7 +2512,7 @@
         <v>65</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q19" s="9">
         <v>46246</v>
@@ -2523,19 +2520,19 @@
       <c r="R19" s="9">
         <v>46245</v>
       </c>
-      <c r="S19" s="12" t="s">
-        <v>67</v>
+      <c r="S19" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
       </c>
       <c r="U19" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B20" s="5">
         <v>46224.69093564815</v>
@@ -2545,7 +2542,7 @@
         <v>46224.72969400463</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2569,7 +2566,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2582,7 +2579,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" s="9">
         <v>46224.69110914352</v>
@@ -2592,16 +2589,16 @@
         <v>46224.88562534722</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="I21" s="9">
         <v>46248</v>
@@ -2619,13 +2616,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q21" s="9">
         <v>46259</v>
@@ -2640,12 +2637,12 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" s="5">
         <v>46224.691113368055</v>
@@ -2655,16 +2652,16 @@
         <v>46224.88573403935</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="I22" s="5">
         <v>46247</v>
@@ -2682,13 +2679,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
@@ -2699,12 +2696,12 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B23" s="9">
         <v>46224.69111763889</v>
@@ -2714,16 +2711,16 @@
         <v>46224.885731030095</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="I23" s="9">
         <v>46251</v>
@@ -2741,13 +2738,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2758,12 +2755,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" s="5">
         <v>46224.691122118056</v>
@@ -2773,16 +2770,16 @@
         <v>46224.88562246528</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="I24" s="5">
         <v>46248</v>
@@ -2800,10 +2797,10 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2821,12 +2818,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B25" s="9">
         <v>46224.69117694444</v>
@@ -2836,16 +2833,16 @@
         <v>46224.88583665509</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="I25" s="9">
         <v>46247</v>
@@ -2863,13 +2860,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2879,7 +2876,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B26" s="5">
         <v>46224.691182546296</v>
@@ -2889,16 +2886,16 @@
         <v>46224.88583366898</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="I26" s="5">
         <v>46251</v>
@@ -2916,13 +2913,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2932,7 +2929,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B27" s="9">
         <v>46224.69118782408</v>
@@ -2942,16 +2939,16 @@
         <v>46224.88561925926</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="I27" s="9">
         <v>46248</v>
@@ -2969,10 +2966,10 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -2990,12 +2987,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B28" s="5">
         <v>46224.69119221065</v>
@@ -3005,16 +3002,16 @@
         <v>46224.88591563657</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -3032,13 +3029,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3048,7 +3045,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B29" s="9">
         <v>46224.69119738426</v>
@@ -3058,16 +3055,16 @@
         <v>46224.88591252315</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="I29" s="9">
         <v>46251</v>
@@ -3085,13 +3082,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3101,7 +3098,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B30" s="5">
         <v>46224.72969201389</v>
@@ -3111,16 +3108,16 @@
         <v>46224.88605396991</v>
       </c>
       <c r="E30" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="6" t="s">
+      <c r="H30" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="I30" s="5">
         <v>46260</v>
@@ -3138,10 +3135,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3159,12 +3156,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B31" s="9">
         <v>46224.72978952546</v>
@@ -3174,16 +3171,16 @@
         <v>46237.55371150463</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>110</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>111</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3201,13 +3198,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O31" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="P31" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="P31" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3217,7 +3214,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5">
         <v>46224.72983336805</v>
@@ -3227,16 +3224,16 @@
         <v>46224.886155405096</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="I32" s="5">
         <v>46258</v>
@@ -3254,13 +3251,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3270,7 +3267,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B33" s="9">
         <v>46224.72985208333</v>
@@ -3280,16 +3277,16 @@
         <v>46224.88628099537</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="I33" s="9">
         <v>46289</v>
@@ -3307,13 +3304,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3323,7 +3320,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5">
         <v>46224.690940555556</v>
@@ -3333,7 +3330,7 @@
         <v>46238.48598052083</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>25</v>
@@ -3357,7 +3354,7 @@
         <v>26</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3370,7 +3367,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B35" s="9">
         <v>46224.6912024537</v>
@@ -3382,16 +3379,16 @@
         <v>46235.195113483795</v>
       </c>
       <c r="E35" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I35" s="9">
         <v>46230</v>
@@ -3409,13 +3406,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>43</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q35" s="9">
         <v>46234</v>
@@ -3435,7 +3432,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46224.69120917824</v>
@@ -3447,16 +3444,16 @@
         <v>46242.166817314814</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46237</v>
@@ -3474,13 +3471,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q36" s="5">
         <v>46241</v>
@@ -3500,7 +3497,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" s="9">
         <v>46224.69121665509</v>
@@ -3518,10 +3515,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>137</v>
       </c>
       <c r="I37" s="9">
         <v>46244</v>
@@ -3539,13 +3536,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9">
         <v>46244</v>
@@ -3565,7 +3562,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46224.691245740745</v>
@@ -3575,16 +3572,16 @@
         <v>46224.8865816551</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>142</v>
       </c>
       <c r="I38" s="5">
         <v>46290</v>
@@ -3602,13 +3599,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q38" s="5">
         <v>46290</v>
@@ -3623,12 +3620,12 @@
         <v>0</v>
       </c>
       <c r="U38" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B39" s="9">
         <v>46224.6912528588</v>
@@ -3638,16 +3635,16 @@
         <v>46224.88666928241</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>141</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>142</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="9">
@@ -3663,13 +3660,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O39" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="P39" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="P39" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3679,7 +3676,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46224.691256886574</v>
@@ -3689,16 +3686,16 @@
         <v>46224.88666613426</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>142</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3714,13 +3711,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3730,7 +3727,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B41" s="9">
         <v>46224.69128170139</v>
@@ -3740,16 +3737,16 @@
         <v>46224.886662986115</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>141</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>142</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="9">
@@ -3765,13 +3762,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O41" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="P41" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="P41" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3781,7 +3778,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B42" s="5">
         <v>46224.69139119213</v>
@@ -3791,7 +3788,7 @@
         <v>46224.824914756944</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3815,7 +3812,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3828,7 +3825,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B43" s="9">
         <v>46224.69139565973</v>
@@ -3838,16 +3835,16 @@
         <v>46224.88680275463</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="I43" s="9">
         <v>46260</v>
@@ -3865,13 +3862,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q43" s="9">
         <v>46260</v>
@@ -3886,12 +3883,12 @@
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46224.69140096065</v>
@@ -3901,16 +3898,16 @@
         <v>46224.88679966435</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="I44" s="5">
         <v>46260</v>
@@ -3928,13 +3925,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="5">
         <v>46260</v>
@@ -3949,12 +3946,12 @@
         <v>0</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B45" s="9">
         <v>46224.69140581018</v>
@@ -3964,16 +3961,16 @@
         <v>46224.886796192135</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="I45" s="9">
         <v>46260</v>
@@ -3991,13 +3988,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q45" s="9">
         <v>46260</v>
@@ -4012,12 +4009,12 @@
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B46" s="5">
         <v>46224.691410740736</v>
@@ -4027,16 +4024,16 @@
         <v>46224.88687898148</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I46" s="5">
         <v>46261</v>
@@ -4054,13 +4051,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q46" s="5">
         <v>46261</v>
@@ -4075,12 +4072,12 @@
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B47" s="9">
         <v>46224.69141809028</v>
@@ -4090,16 +4087,16 @@
         <v>46224.886876122684</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="I47" s="9">
         <v>46261</v>
@@ -4117,13 +4114,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="9">
         <v>46261</v>
@@ -4138,12 +4135,12 @@
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46224.69142430555</v>
@@ -4153,16 +4150,16 @@
         <v>46224.88687315972</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4180,13 +4177,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="5">
         <v>46261</v>
@@ -4201,12 +4198,12 @@
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B49" s="9">
         <v>46224.69143046296</v>
@@ -4216,7 +4213,7 @@
         <v>46224.835371608795</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4240,7 +4237,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4253,7 +4250,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46224.6914341088</v>
@@ -4263,16 +4260,16 @@
         <v>46224.88693119213</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I50" s="5">
         <v>46262</v>
@@ -4290,13 +4287,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q50" s="5">
         <v>46266</v>
@@ -4311,12 +4308,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B51" s="9">
         <v>46224.69144137732</v>
@@ -4326,16 +4323,16 @@
         <v>46224.887193206014</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I51" s="9">
         <v>46267</v>
@@ -4353,13 +4350,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q51" s="9">
         <v>46273</v>
@@ -4374,12 +4371,12 @@
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B52" s="5">
         <v>46224.69144840278</v>
@@ -4389,16 +4386,16 @@
         <v>46238.485980983794</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I52" s="5">
         <v>46267</v>
@@ -4416,13 +4413,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4432,7 +4429,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B53" s="9">
         <v>46224.691457141205</v>
@@ -4442,16 +4439,16 @@
         <v>46238.48598550926</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I53" s="9">
         <v>46267</v>
@@ -4469,13 +4466,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O53" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="P53" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="P53" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4485,7 +4482,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B54" s="5">
         <v>46224.69146548611</v>
@@ -4495,16 +4492,16 @@
         <v>46238.48598592593</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I54" s="5">
         <v>46267</v>
@@ -4522,13 +4519,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4538,7 +4535,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B55" s="9">
         <v>46224.691625312495</v>
@@ -4548,16 +4545,16 @@
         <v>46224.88734793982</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I55" s="9">
         <v>46274</v>
@@ -4575,13 +4572,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q55" s="9">
         <v>46274</v>
@@ -4596,12 +4593,12 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B56" s="5">
         <v>46224.69163763888</v>
@@ -4611,16 +4608,16 @@
         <v>46238.485983136576</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I56" s="5">
         <v>46274</v>
@@ -4638,13 +4635,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4654,7 +4651,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B57" s="9">
         <v>46224.69164405092</v>
@@ -4664,16 +4661,16 @@
         <v>46238.48598453704</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I57" s="9">
         <v>46274</v>
@@ -4691,13 +4688,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O57" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="P57" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="P57" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4707,7 +4704,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B58" s="5">
         <v>46224.69164984954</v>
@@ -4717,16 +4714,16 @@
         <v>46238.485981562495</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I58" s="5">
         <v>46274</v>
@@ -4744,13 +4741,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4760,7 +4757,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B59" s="9">
         <v>46224.69178202546</v>
@@ -4770,7 +4767,7 @@
         <v>46224.83612613426</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -4794,7 +4791,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -4807,7 +4804,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B60" s="5">
         <v>46224.691786446754</v>
@@ -4817,16 +4814,16 @@
         <v>46237.55364837963</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="I60" s="5">
         <v>46230</v>
@@ -4844,13 +4841,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>50</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q60" s="5">
         <v>46231</v>
@@ -4865,12 +4862,12 @@
         <v>0</v>
       </c>
       <c r="U60" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B61" s="9">
         <v>46224.69179621528</v>
@@ -4880,16 +4877,16 @@
         <v>46237.55356576389</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="I61" s="9">
         <v>46230</v>
@@ -4907,13 +4904,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q61" s="9">
         <v>46231</v>
@@ -4928,12 +4925,12 @@
         <v>0</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B62" s="5">
         <v>46224.691807152776</v>
@@ -4943,16 +4940,16 @@
         <v>46237.55362008102</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="I62" s="5">
         <v>46230</v>
@@ -4970,13 +4967,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>59</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q62" s="5">
         <v>46231</v>
@@ -4991,12 +4988,12 @@
         <v>0</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B63" s="9">
         <v>46224.69181694444</v>
@@ -5006,7 +5003,7 @@
         <v>46232.60338635417</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>25</v>
@@ -5030,7 +5027,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5043,7 +5040,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B64" s="5">
         <v>46224.69182049768</v>
@@ -5053,7 +5050,7 @@
         <v>46232.624381828704</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5080,13 +5077,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q64" s="5">
         <v>46281</v>
@@ -5101,12 +5098,12 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B65" s="9">
         <v>46224.691826967595</v>
@@ -5116,7 +5113,7 @@
         <v>46224.887663622685</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5143,13 +5140,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5159,7 +5156,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B66" s="5">
         <v>46224.691831840275</v>
@@ -5169,7 +5166,7 @@
         <v>46224.8876609375</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5196,13 +5193,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5212,7 +5209,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B67" s="9">
         <v>46224.69183667824</v>
@@ -5222,7 +5219,7 @@
         <v>46224.8876578125</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5249,13 +5246,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5265,7 +5262,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B68" s="5">
         <v>46224.69195275463</v>
@@ -5275,7 +5272,7 @@
         <v>46232.62438170139</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5302,13 +5299,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>221</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>222</v>
       </c>
       <c r="Q68" s="5">
         <v>46286</v>
@@ -5323,12 +5320,12 @@
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B69" s="9">
         <v>46224.69195878472</v>
@@ -5338,7 +5335,7 @@
         <v>46238.48598511574</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5365,13 +5362,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5381,7 +5378,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B70" s="5">
         <v>46224.69196560185</v>
@@ -5391,7 +5388,7 @@
         <v>46238.48598628472</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5418,13 +5415,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5434,7 +5431,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B71" s="9">
         <v>46224.69197195602</v>
@@ -5444,7 +5441,7 @@
         <v>46238.485982094906</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5471,13 +5468,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5487,7 +5484,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B72" s="5">
         <v>46224.6920590625</v>
@@ -5497,7 +5494,7 @@
         <v>46232.62438170139</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5524,13 +5521,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="Q72" s="5">
         <v>46287</v>
@@ -5545,12 +5542,12 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B73" s="9">
         <v>46224.69206486111</v>
@@ -5560,7 +5557,7 @@
         <v>46224.888117256945</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5587,13 +5584,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O73" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="P73" s="10" t="s">
         <v>235</v>
-      </c>
-      <c r="P73" s="10" t="s">
-        <v>236</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5603,7 +5600,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B74" s="5">
         <v>46224.69207089121</v>
@@ -5613,7 +5610,7 @@
         <v>46224.88811447917</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5640,13 +5637,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5656,7 +5653,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B75" s="9">
         <v>46224.69207630787</v>
@@ -5666,7 +5663,7 @@
         <v>46224.88811143518</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5693,13 +5690,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5709,7 +5706,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B76" s="5">
         <v>46224.692210925925</v>
@@ -5719,7 +5716,7 @@
         <v>46240.822117592594</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5746,13 +5743,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q76" s="5">
         <v>46288</v>
@@ -5767,12 +5764,12 @@
         <v>0</v>
       </c>
       <c r="U76" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B77" s="9">
         <v>46224.69221851852</v>
@@ -5782,7 +5779,7 @@
         <v>46238.48598354167</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5809,13 +5806,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O77" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="P77" s="10" t="s">
         <v>244</v>
-      </c>
-      <c r="P77" s="10" t="s">
-        <v>245</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5825,7 +5822,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B78" s="5">
         <v>46224.692225335646</v>
@@ -5835,7 +5832,7 @@
         <v>46238.48598415509</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5862,13 +5859,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5878,7 +5875,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B79" s="9">
         <v>46224.69223655092</v>
@@ -5888,7 +5885,7 @@
         <v>46224.88821421296</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -5915,13 +5912,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -5931,7 +5928,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B80" s="5">
         <v>46224.69235351852</v>
@@ -5941,7 +5938,7 @@
         <v>46240.822117662035</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -5968,13 +5965,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q80" s="5">
         <v>46289</v>
@@ -5989,12 +5986,12 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B81" s="9">
         <v>46224.6923596875</v>
@@ -6004,7 +6001,7 @@
         <v>46224.88831505787</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6031,13 +6028,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6047,7 +6044,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B82" s="5">
         <v>46224.69236840278</v>
@@ -6057,7 +6054,7 @@
         <v>46224.88831152778</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6084,13 +6081,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6100,7 +6097,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B83" s="9">
         <v>46224.69237796296</v>
@@ -6110,7 +6107,7 @@
         <v>46224.88830864584</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6137,13 +6134,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6153,7 +6150,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B84" s="5">
         <v>46224.69253115741</v>
@@ -6163,7 +6160,7 @@
         <v>46232.62438199074</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6190,13 +6187,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O84" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="P84" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="Q84" s="5">
         <v>46293</v>
@@ -6211,12 +6208,12 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B85" s="9">
         <v>46224.69253806713</v>
@@ -6226,7 +6223,7 @@
         <v>46224.88840122685</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6251,13 +6248,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6267,7 +6264,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B86" s="5">
         <v>46224.69254259259</v>
@@ -6277,7 +6274,7 @@
         <v>46224.88839846065</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6302,13 +6299,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6318,7 +6315,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B87" s="9">
         <v>46224.69254695602</v>
@@ -6328,7 +6325,7 @@
         <v>46224.888395601854</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6353,13 +6350,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6369,7 +6366,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B88" s="5">
         <v>46224.69261697917</v>
@@ -6379,7 +6376,7 @@
         <v>46224.88265856481</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>25</v>
@@ -6403,7 +6400,7 @@
         <v>26</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -6416,7 +6413,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B89" s="9">
         <v>46224.69265170139</v>
@@ -6426,16 +6423,16 @@
         <v>46224.888549525465</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>268</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>269</v>
       </c>
       <c r="I89" s="9">
         <v>46294</v>
@@ -6453,13 +6450,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q89" s="9">
         <v>46294</v>
@@ -6474,12 +6471,12 @@
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B90" s="5">
         <v>46224.69265774306</v>
@@ -6489,16 +6486,16 @@
         <v>46224.88851116898</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="I90" s="5">
         <v>46294</v>
@@ -6516,13 +6513,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6532,7 +6529,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B91" s="9">
         <v>46224.69266123843</v>
@@ -6542,16 +6539,16 @@
         <v>46224.8885084838</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>268</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>269</v>
       </c>
       <c r="I91" s="9">
         <v>46294</v>
@@ -6569,13 +6566,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6585,7 +6582,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B92" s="5">
         <v>46224.692664456015</v>
@@ -6595,16 +6592,16 @@
         <v>46224.88850347222</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="I92" s="5">
         <v>46294</v>
@@ -6622,13 +6619,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6638,7 +6635,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B93" s="9">
         <v>46224.69271221065</v>
@@ -6648,7 +6645,7 @@
         <v>46224.88867554398</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6675,13 +6672,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q93" s="9">
         <v>46295</v>
@@ -6696,12 +6693,12 @@
         <v>0</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B94" s="5">
         <v>46224.69271712963</v>
@@ -6711,7 +6708,7 @@
         <v>46224.888643495375</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6736,13 +6733,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6752,7 +6749,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B95" s="9">
         <v>46224.692723113425</v>
@@ -6762,7 +6759,7 @@
         <v>46224.88864100694</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6787,13 +6784,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6803,7 +6800,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B96" s="5">
         <v>46224.692728483795</v>
@@ -6813,7 +6810,7 @@
         <v>46224.88863769676</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6838,13 +6835,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6854,7 +6851,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B97" s="9">
         <v>46224.692771875</v>
@@ -6864,16 +6861,16 @@
         <v>46224.88885393519</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I97" s="9">
         <v>46296</v>
@@ -6891,13 +6888,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q97" s="9">
         <v>46296</v>
@@ -6912,12 +6909,12 @@
         <v>0</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B98" s="5">
         <v>46224.69280849537</v>
@@ -6927,16 +6924,16 @@
         <v>46224.88880863426</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I98" s="5">
         <v>46296</v>
@@ -6954,13 +6951,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -6970,7 +6967,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B99" s="9">
         <v>46224.69281277778</v>
@@ -6980,16 +6977,16 @@
         <v>46224.888805462964</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I99" s="9">
         <v>46296</v>
@@ -7007,13 +7004,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7023,7 +7020,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B100" s="5">
         <v>46224.69281645834</v>
@@ -7033,16 +7030,16 @@
         <v>46224.88880255787</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I100" s="5">
         <v>46296</v>
@@ -7060,13 +7057,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7076,7 +7073,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B101" s="9">
         <v>46224.692877442125</v>
@@ -7086,16 +7083,16 @@
         <v>46224.88918993056</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I101" s="9">
         <v>46297</v>
@@ -7113,13 +7110,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q101" s="9">
         <v>46297</v>
@@ -7134,12 +7131,12 @@
         <v>0</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B102" s="5">
         <v>46224.69288434028</v>
@@ -7149,16 +7146,16 @@
         <v>46224.88913273148</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I102" s="5">
         <v>46297</v>
@@ -7176,13 +7173,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7192,7 +7189,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B103" s="9">
         <v>46224.69288743056</v>
@@ -7202,16 +7199,16 @@
         <v>46224.8891297338</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I103" s="9">
         <v>46297</v>
@@ -7229,13 +7226,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7245,7 +7242,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B104" s="5">
         <v>46224.692890509265</v>
@@ -7255,16 +7252,16 @@
         <v>46224.88912665509</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I104" s="5">
         <v>46297</v>
@@ -7282,13 +7279,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7298,7 +7295,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B105" s="9">
         <v>46224.692977743056</v>
@@ -7308,7 +7305,7 @@
         <v>46224.88292137731</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>25</v>
@@ -7332,7 +7329,7 @@
         <v>26</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>26</v>
@@ -7345,7 +7342,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B106" s="5">
         <v>46224.69298071759</v>
@@ -7355,16 +7352,16 @@
         <v>46224.88926996528</v>
       </c>
       <c r="E106" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G106" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="F106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G106" s="6" t="s">
+      <c r="H106" s="6" t="s">
         <v>298</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>299</v>
       </c>
       <c r="I106" s="5">
         <v>46300</v>
@@ -7382,13 +7379,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q106" s="5">
         <v>46304</v>
@@ -7403,12 +7400,12 @@
         <v>0</v>
       </c>
       <c r="U106" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B107" s="9">
         <v>46224.693000983796</v>
@@ -7418,7 +7415,7 @@
         <v>46224.88933664352</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7445,13 +7442,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q107" s="9">
         <v>46304</v>
@@ -7466,7 +7463,7 @@
         <v>0</v>
       </c>
       <c r="U107" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46224.88573403935</v>
+        <v>46248.17129400463</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>86</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46224.88583665509</v>
+        <v>46248.17129546296</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>70</v>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46224.88591563657</v>
+        <v>46248.17129215278</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>76</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -3108,7 +3108,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46224.88605396991</v>
+        <v>46253.17656765046</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>109</v>
@@ -3152,8 +3152,8 @@
       <c r="R30" s="5">
         <v>46260</v>
       </c>
-      <c r="S30" s="7" t="s">
-        <v>32</v>
+      <c r="S30" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46224.88680275463</v>
+        <v>46253.17656763889</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>154</v>
@@ -3879,8 +3879,8 @@
       <c r="R43" s="9">
         <v>46260</v>
       </c>
-      <c r="S43" s="7" t="s">
-        <v>32</v>
+      <c r="S43" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46224.88679966435</v>
+        <v>46253.17656761574</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>159</v>
@@ -3942,8 +3942,8 @@
       <c r="R44" s="5">
         <v>46260</v>
       </c>
-      <c r="S44" s="7" t="s">
-        <v>32</v>
+      <c r="S44" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46224.886796192135</v>
+        <v>46253.17656868056</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>162</v>
@@ -4005,8 +4005,8 @@
       <c r="R45" s="9">
         <v>46260</v>
       </c>
-      <c r="S45" s="7" t="s">
-        <v>32</v>
+      <c r="S45" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -4024,7 +4024,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46224.88687898148</v>
+        <v>46254.20419275463</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>165</v>
@@ -4068,8 +4068,8 @@
       <c r="R46" s="5">
         <v>46261</v>
       </c>
-      <c r="S46" s="7" t="s">
-        <v>32</v>
+      <c r="S46" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46224.886876122684</v>
+        <v>46254.2041925</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>168</v>
@@ -4131,8 +4131,8 @@
       <c r="R47" s="9">
         <v>46261</v>
       </c>
-      <c r="S47" s="7" t="s">
-        <v>32</v>
+      <c r="S47" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46224.88687315972</v>
+        <v>46254.204191736106</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>171</v>
@@ -4194,8 +4194,8 @@
       <c r="R48" s="5">
         <v>46261</v>
       </c>
-      <c r="S48" s="7" t="s">
-        <v>32</v>
+      <c r="S48" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -380,7 +380,7 @@
     <t>Generacion Oc  OT 4375</t>
   </si>
   <si>
-    <t xml:space="preserve">propuesta fabricación externa </t>
+    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
   </si>
   <si>
     <t>Armado OT 4375,Fabricación externa  OT 4375</t>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46237.55371150463</v>
+        <v>46254.64730673611</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>114</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -3171,7 +3171,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46254.64730673611</v>
+        <v>46255.17014818287</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>114</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -3171,7 +3171,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46255.17014818287</v>
+        <v>46255.62865179398</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>114</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -2589,7 +2589,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46252.178454270834</v>
+        <v>46259.16926409722</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>79</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46224.885731030095</v>
+        <v>46259.16926079861</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>90</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46252.17845412037</v>
+        <v>46259.16926197917</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>93</v>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46224.88583366898</v>
+        <v>46259.169263020834</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46252.178454189816</v>
+        <v>46259.16925892361</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>101</v>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46224.88591252315</v>
+        <v>46259.16925576389</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>106</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46224.88693119213</v>
+        <v>46259.196451296295</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>73</v>
@@ -4304,8 +4304,8 @@
       <c r="R50" s="5">
         <v>46231</v>
       </c>
-      <c r="S50" s="7" t="s">
-        <v>32</v>
+      <c r="S50" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -287,91 +287,91 @@
     <t>Generación OC corte laser  OT 4375,Fabricacion corte laser OT 4375</t>
   </si>
   <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1216762958489039</t>
+  </si>
+  <si>
+    <t>Generación OC corte laser  OT 4375</t>
+  </si>
+  <si>
+    <t>Corte Laser  OT 4375,Fabricacion corte laser OT 4375</t>
+  </si>
+  <si>
+    <t>1216762958489057</t>
+  </si>
+  <si>
+    <t>Fabricacion corte laser OT 4375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte Laser  OT 4375,Recepcion corte laser  OT 4375 </t>
+  </si>
+  <si>
+    <t>1216762958496467</t>
+  </si>
+  <si>
+    <t>Corte plasma  OT 4375</t>
+  </si>
+  <si>
+    <t>Fabricación corte plasma  OT 4375,Generacion OC Corte plasma  OT 4375</t>
+  </si>
+  <si>
+    <t>1216762958532661</t>
+  </si>
+  <si>
+    <t>Corte plasma  OT 4375,Fabricación corte plasma  OT 4375</t>
+  </si>
+  <si>
+    <t>1216762958532676</t>
+  </si>
+  <si>
+    <t>Fabricación corte plasma  OT 4375</t>
+  </si>
+  <si>
+    <t>Corte plasma  OT 4375,Recepcion corte plasma  OT 4375</t>
+  </si>
+  <si>
+    <t>1216762846389708</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4375</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4375,Generación OC mecanizado OT 4375</t>
+  </si>
+  <si>
+    <t>1216762846389718</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4375,Mecanizado OT 4375</t>
+  </si>
+  <si>
+    <t>1216762727289060</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4375</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4375,Recepcion mecanizado OT 4375</t>
+  </si>
+  <si>
+    <t>1216730497556494</t>
+  </si>
+  <si>
+    <t>Fabricación externa  OT 4375</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion Oc  OT 4375,Armado OT 4375,Control de calidad  OT 4375</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1216762958489039</t>
-  </si>
-  <si>
-    <t>Generación OC corte laser  OT 4375</t>
-  </si>
-  <si>
-    <t>Corte Laser  OT 4375,Fabricacion corte laser OT 4375</t>
-  </si>
-  <si>
-    <t>1216762958489057</t>
-  </si>
-  <si>
-    <t>Fabricacion corte laser OT 4375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte Laser  OT 4375,Recepcion corte laser  OT 4375 </t>
-  </si>
-  <si>
-    <t>1216762958496467</t>
-  </si>
-  <si>
-    <t>Corte plasma  OT 4375</t>
-  </si>
-  <si>
-    <t>Fabricación corte plasma  OT 4375,Generacion OC Corte plasma  OT 4375</t>
-  </si>
-  <si>
-    <t>1216762958532661</t>
-  </si>
-  <si>
-    <t>Corte plasma  OT 4375,Fabricación corte plasma  OT 4375</t>
-  </si>
-  <si>
-    <t>1216762958532676</t>
-  </si>
-  <si>
-    <t>Fabricación corte plasma  OT 4375</t>
-  </si>
-  <si>
-    <t>Corte plasma  OT 4375,Recepcion corte plasma  OT 4375</t>
-  </si>
-  <si>
-    <t>1216762846389708</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4375</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4375,Generación OC mecanizado OT 4375</t>
-  </si>
-  <si>
-    <t>1216762846389718</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4375,Mecanizado OT 4375</t>
-  </si>
-  <si>
-    <t>1216762727289060</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4375</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4375,Recepcion mecanizado OT 4375</t>
-  </si>
-  <si>
-    <t>1216730497556494</t>
-  </si>
-  <si>
-    <t>Fabricación externa  OT 4375</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion Oc  OT 4375,Armado OT 4375,Control de calidad  OT 4375</t>
   </si>
   <si>
     <t>1216730497556495</t>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46259.16926409722</v>
+        <v>46260.20736539352</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>79</v>
@@ -2633,19 +2633,19 @@
       <c r="R21" s="9">
         <v>46248</v>
       </c>
-      <c r="S21" s="12" t="s">
-        <v>84</v>
+      <c r="S21" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T21" s="10">
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" s="5">
         <v>46224.691113368055</v>
@@ -2655,7 +2655,7 @@
         <v>46248.17129400463</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2688,7 +2688,7 @@
         <v>63</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
@@ -2699,12 +2699,12 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B23" s="9">
         <v>46224.69111763889</v>
@@ -2714,7 +2714,7 @@
         <v>46259.16926079861</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2744,10 +2744,10 @@
         <v>79</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2758,22 +2758,22 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" s="5">
         <v>46224.691122118056</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46259.16926197917</v>
+        <v>46260.20736489583</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2803,7 +2803,7 @@
         <v>78</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2814,19 +2814,19 @@
       <c r="R24" s="5">
         <v>46248</v>
       </c>
-      <c r="S24" s="12" t="s">
-        <v>84</v>
+      <c r="S24" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B25" s="9">
         <v>46224.69117694444</v>
@@ -2863,13 +2863,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>69</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2879,7 +2879,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B26" s="5">
         <v>46224.691182546296</v>
@@ -2889,7 +2889,7 @@
         <v>46259.169263020834</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -2916,13 +2916,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>70</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2932,17 +2932,17 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B27" s="9">
         <v>46224.69118782408</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46259.16925892361</v>
+        <v>46260.20737615741</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -2972,7 +2972,7 @@
         <v>78</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -2983,19 +2983,19 @@
       <c r="R27" s="9">
         <v>46248</v>
       </c>
-      <c r="S27" s="12" t="s">
-        <v>84</v>
+      <c r="S27" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B28" s="5">
         <v>46224.69119221065</v>
@@ -3032,13 +3032,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B29" s="9">
         <v>46224.69119738426</v>
@@ -3058,7 +3058,7 @@
         <v>46259.16925576389</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
@@ -3085,13 +3085,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>76</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3101,26 +3101,26 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B30" s="5">
         <v>46224.72969201389</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46253.17656765046</v>
+        <v>46260.169244942124</v>
       </c>
       <c r="E30" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="6" t="s">
+      <c r="H30" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="I30" s="5">
         <v>46260</v>
@@ -3141,7 +3141,7 @@
         <v>78</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3153,13 +3153,13 @@
         <v>46260</v>
       </c>
       <c r="S30" s="12" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3180,10 +3180,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>110</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>111</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3201,7 +3201,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>115</v>
@@ -3233,10 +3233,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="I32" s="5">
         <v>46258</v>
@@ -3254,7 +3254,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>114</v>
@@ -3307,13 +3307,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>118</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3623,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="U38" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46253.17656763889</v>
+        <v>46260.16926087963</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>154</v>
@@ -3868,7 +3868,7 @@
         <v>151</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>157</v>
@@ -3880,13 +3880,13 @@
         <v>46260</v>
       </c>
       <c r="S43" s="12" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46253.17656761574</v>
+        <v>46260.169257650465</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>159</v>
@@ -3931,7 +3931,7 @@
         <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>160</v>
@@ -3943,13 +3943,13 @@
         <v>46260</v>
       </c>
       <c r="S44" s="12" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46253.17656868056</v>
+        <v>46260.169259594906</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>162</v>
@@ -3994,7 +3994,7 @@
         <v>151</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>163</v>
@@ -4006,13 +4006,13 @@
         <v>46260</v>
       </c>
       <c r="S45" s="12" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4069,13 +4069,13 @@
         <v>46261</v>
       </c>
       <c r="S46" s="12" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4132,13 +4132,13 @@
         <v>46261</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4195,13 +4195,13 @@
         <v>46261</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4305,13 +4305,13 @@
         <v>46231</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4374,7 +4374,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4596,7 +4596,7 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5323,7 +5323,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5545,7 +5545,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5767,7 +5767,7 @@
         <v>0</v>
       </c>
       <c r="U76" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -5989,7 +5989,7 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6211,7 +6211,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6474,7 +6474,7 @@
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -6696,7 +6696,7 @@
         <v>0</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -6912,7 +6912,7 @@
         <v>0</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7134,7 +7134,7 @@
         <v>0</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7403,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="U106" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -7466,7 +7466,7 @@
         <v>0</v>
       </c>
       <c r="U107" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46259.196451296295</v>
+        <v>46260.588653240746</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>73</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -371,169 +371,169 @@
     <t>Generacion Oc  OT 4375,Armado OT 4375,Control de calidad  OT 4375</t>
   </si>
   <si>
+    <t>1216730497556495</t>
+  </si>
+  <si>
+    <t>Generacion Oc  OT 4375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
+  </si>
+  <si>
+    <t>Armado OT 4375,Fabricación externa  OT 4375</t>
+  </si>
+  <si>
+    <t>1216730497556496</t>
+  </si>
+  <si>
+    <t>Armado OT 4375</t>
+  </si>
+  <si>
+    <t>Control de calidad  OT 4375,Fabricación externa  OT 4375</t>
+  </si>
+  <si>
+    <t>1216730497556497</t>
+  </si>
+  <si>
+    <t>Control de calidad  OT 4375</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1216730497556438</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Plano Preliminar OT 4375,Check Planos OT 4375,Check pruebas FAT OT 4375,Plano Definitivos OT 4375</t>
+  </si>
+  <si>
+    <t>1216762727289075</t>
+  </si>
+  <si>
+    <t>Plano Preliminar OT 4375</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Plano Definitivos OT 4375</t>
+  </si>
+  <si>
+    <t>1216762846409976</t>
+  </si>
+  <si>
+    <t>Plano Definitivos OT 4375</t>
+  </si>
+  <si>
+    <t>Check Planos OT 4375,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1216762846410001</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa   OT 4375,Propuesta Mecanizado OT 4375,Propuesta Corte plasma  OT 4375,propuesta Corte laser OT 4375,Ingenieria y diseñoo:,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216762727308398</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT OT 4375</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216762727308413</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216762727308423</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Check pruebas FAT OT 4375,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,OT 4347 Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1216762958655976</t>
+  </si>
+  <si>
+    <t>1216763090561498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega </t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma OT 4375 ,Recepcion corte plasma  OT 4375,Recepcion mecanizado OT 4375,Control de calidad corte Laser OT 4375,Recepcion corte laser  OT 4375 ,Control de calidad Mecanizado OT 4375</t>
+  </si>
+  <si>
+    <t>1216763090561510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte laser  OT 4375 </t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte Laser OT 4375,Bodega </t>
+  </si>
+  <si>
+    <t>1216762958767366</t>
+  </si>
+  <si>
+    <t>Recepcion corte plasma  OT 4375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma OT 4375 ,Bodega </t>
+  </si>
+  <si>
+    <t>1216762958767386</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado OT 4375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado OT 4375,Bodega </t>
+  </si>
+  <si>
+    <t>1216762958784986</t>
+  </si>
+  <si>
+    <t>Control de calidad corte Laser OT 4375</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Bodega ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216730497556495</t>
-  </si>
-  <si>
-    <t>Generacion Oc  OT 4375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
-  </si>
-  <si>
-    <t>Armado OT 4375,Fabricación externa  OT 4375</t>
-  </si>
-  <si>
-    <t>1216730497556496</t>
-  </si>
-  <si>
-    <t>Armado OT 4375</t>
-  </si>
-  <si>
-    <t>Control de calidad  OT 4375,Fabricación externa  OT 4375</t>
-  </si>
-  <si>
-    <t>1216730497556497</t>
-  </si>
-  <si>
-    <t>Control de calidad  OT 4375</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1216730497556438</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Plano Preliminar OT 4375,Check Planos OT 4375,Check pruebas FAT OT 4375,Plano Definitivos OT 4375</t>
-  </si>
-  <si>
-    <t>1216762727289075</t>
-  </si>
-  <si>
-    <t>Plano Preliminar OT 4375</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Plano Definitivos OT 4375</t>
-  </si>
-  <si>
-    <t>1216762846409976</t>
-  </si>
-  <si>
-    <t>Plano Definitivos OT 4375</t>
-  </si>
-  <si>
-    <t>Check Planos OT 4375,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1216762846410001</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa   OT 4375,Propuesta Mecanizado OT 4375,Propuesta Corte plasma  OT 4375,propuesta Corte laser OT 4375,Ingenieria y diseñoo:,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216762727308398</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT OT 4375</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216762727308413</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216762727308423</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Check pruebas FAT OT 4375,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,OT 4347 Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1216762958655976</t>
-  </si>
-  <si>
-    <t>1216763090561498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega </t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma OT 4375 ,Recepcion corte plasma  OT 4375,Recepcion mecanizado OT 4375,Control de calidad corte Laser OT 4375,Recepcion corte laser  OT 4375 ,Control de calidad Mecanizado OT 4375</t>
-  </si>
-  <si>
-    <t>1216763090561510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte laser  OT 4375 </t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte Laser OT 4375,Bodega </t>
-  </si>
-  <si>
-    <t>1216762958767366</t>
-  </si>
-  <si>
-    <t>Recepcion corte plasma  OT 4375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma OT 4375 ,Bodega </t>
-  </si>
-  <si>
-    <t>1216762958767386</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado OT 4375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado OT 4375,Bodega </t>
-  </si>
-  <si>
-    <t>1216762958784986</t>
-  </si>
-  <si>
-    <t>Control de calidad corte Laser OT 4375</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Bodega ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1216762727441897</t>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46260.169244942124</v>
+        <v>46261.190973668985</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>108</v>
@@ -3152,8 +3152,8 @@
       <c r="R30" s="5">
         <v>46260</v>
       </c>
-      <c r="S30" s="12" t="s">
-        <v>112</v>
+      <c r="S30" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3164,7 +3164,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B31" s="9">
         <v>46224.72978952546</v>
@@ -3174,7 +3174,7 @@
         <v>46255.62865179398</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3204,10 +3204,10 @@
         <v>108</v>
       </c>
       <c r="O31" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="P31" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="P31" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3217,7 +3217,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5">
         <v>46224.72983336805</v>
@@ -3227,7 +3227,7 @@
         <v>46224.886155405096</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3257,10 +3257,10 @@
         <v>108</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3270,7 +3270,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B33" s="9">
         <v>46224.72985208333</v>
@@ -3280,16 +3280,16 @@
         <v>46224.88628099537</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="I33" s="9">
         <v>46289</v>
@@ -3310,7 +3310,7 @@
         <v>108</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>108</v>
@@ -3323,7 +3323,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5">
         <v>46224.690940555556</v>
@@ -3333,7 +3333,7 @@
         <v>46238.48598052083</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>25</v>
@@ -3357,7 +3357,7 @@
         <v>26</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B35" s="9">
         <v>46224.6912024537</v>
@@ -3382,16 +3382,16 @@
         <v>46235.195113483795</v>
       </c>
       <c r="E35" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I35" s="9">
         <v>46230</v>
@@ -3409,13 +3409,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>43</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q35" s="9">
         <v>46234</v>
@@ -3435,7 +3435,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46224.69120917824</v>
@@ -3447,16 +3447,16 @@
         <v>46242.166817314814</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46237</v>
@@ -3474,13 +3474,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q36" s="5">
         <v>46241</v>
@@ -3500,7 +3500,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" s="9">
         <v>46224.69121665509</v>
@@ -3518,10 +3518,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>137</v>
       </c>
       <c r="I37" s="9">
         <v>46244</v>
@@ -3539,13 +3539,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9">
         <v>46244</v>
@@ -3565,7 +3565,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46224.691245740745</v>
@@ -3575,16 +3575,16 @@
         <v>46224.8865816551</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>142</v>
       </c>
       <c r="I38" s="5">
         <v>46290</v>
@@ -3602,13 +3602,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q38" s="5">
         <v>46290</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B39" s="9">
         <v>46224.6912528588</v>
@@ -3638,16 +3638,16 @@
         <v>46224.88666928241</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>141</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>142</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="9">
@@ -3663,13 +3663,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O39" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="P39" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="P39" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3679,7 +3679,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46224.691256886574</v>
@@ -3689,16 +3689,16 @@
         <v>46224.88666613426</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>142</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3714,13 +3714,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3730,7 +3730,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B41" s="9">
         <v>46224.69128170139</v>
@@ -3740,16 +3740,16 @@
         <v>46224.886662986115</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>141</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>142</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="9">
@@ -3765,13 +3765,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O41" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="P41" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="P41" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3781,17 +3781,17 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B42" s="5">
         <v>46224.69139119213</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46224.824914756944</v>
+        <v>46261.499713020836</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3815,7 +3815,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3828,26 +3828,26 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B43" s="9">
         <v>46224.69139565973</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46260.16926087963</v>
+        <v>46261.19097289351</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="I43" s="9">
         <v>46260</v>
@@ -3865,13 +3865,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>89</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q43" s="9">
         <v>46260</v>
@@ -3879,8 +3879,8 @@
       <c r="R43" s="9">
         <v>46260</v>
       </c>
-      <c r="S43" s="12" t="s">
-        <v>112</v>
+      <c r="S43" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
@@ -3891,26 +3891,26 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46224.69140096065</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46260.169257650465</v>
+        <v>46261.190972337965</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="I44" s="5">
         <v>46260</v>
@@ -3928,13 +3928,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="5">
         <v>46260</v>
@@ -3942,8 +3942,8 @@
       <c r="R44" s="5">
         <v>46260</v>
       </c>
-      <c r="S44" s="12" t="s">
-        <v>112</v>
+      <c r="S44" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
@@ -3954,26 +3954,26 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B45" s="9">
         <v>46224.69140581018</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46260.169259594906</v>
+        <v>46261.190972337965</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="I45" s="9">
         <v>46260</v>
@@ -3991,13 +3991,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>105</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q45" s="9">
         <v>46260</v>
@@ -4005,8 +4005,8 @@
       <c r="R45" s="9">
         <v>46260</v>
       </c>
-      <c r="S45" s="12" t="s">
-        <v>112</v>
+      <c r="S45" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>
@@ -4017,26 +4017,26 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B46" s="5">
         <v>46224.691410740736</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46254.20419275463</v>
+        <v>46261.1686759838</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I46" s="5">
         <v>46261</v>
@@ -4054,13 +4054,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q46" s="5">
         <v>46261</v>
@@ -4069,7 +4069,7 @@
         <v>46261</v>
       </c>
       <c r="S46" s="12" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -4085,9 +4085,11 @@
       <c r="B47" s="9">
         <v>46224.69141809028</v>
       </c>
-      <c r="C47" s="10"/>
+      <c r="C47" s="9">
+        <v>46261.499706030096</v>
+      </c>
       <c r="D47" s="9">
-        <v>46254.2041925</v>
+        <v>46261.49972283565</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>168</v>
@@ -4096,10 +4098,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="I47" s="9">
         <v>46261</v>
@@ -4117,10 +4119,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>169</v>
@@ -4132,13 +4134,13 @@
         <v>46261</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="T47" s="10">
-        <v>0</v>
-      </c>
-      <c r="U47" s="11" t="s">
-        <v>84</v>
+        <v>1</v>
+      </c>
+      <c r="U47" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4150,7 +4152,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46254.204191736106</v>
+        <v>46261.16867167824</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>171</v>
@@ -4159,10 +4161,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4180,10 +4182,10 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>172</v>
@@ -4195,7 +4197,7 @@
         <v>46261</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4260,7 +4262,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46260.588653240746</v>
+        <v>46261.58820892361</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>73</v>
@@ -4305,7 +4307,7 @@
         <v>46231</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4326,7 +4328,7 @@
         <v>46224.887193206014</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4356,7 +4358,7 @@
         <v>174</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>174</v>
@@ -4386,10 +4388,10 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46238.485980983794</v>
+        <v>46261.499713680554</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4416,7 +4418,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>182</v>
@@ -4439,10 +4441,10 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46238.48598550926</v>
+        <v>46261.49971425926</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4469,7 +4471,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>185</v>
@@ -4492,10 +4494,10 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46238.48598592593</v>
+        <v>46261.499714826394</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4522,7 +4524,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>188</v>
@@ -4578,7 +4580,7 @@
         <v>174</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>174</v>
@@ -4611,7 +4613,7 @@
         <v>46238.485983136576</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4664,7 +4666,7 @@
         <v>46238.48598453704</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4717,7 +4719,7 @@
         <v>46238.485981562495</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4823,10 +4825,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="I60" s="5">
         <v>46230</v>
@@ -4886,10 +4888,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="I61" s="9">
         <v>46230</v>
@@ -4949,10 +4951,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="I62" s="5">
         <v>46230</v>
@@ -5083,7 +5085,7 @@
         <v>209</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>213</v>
@@ -5116,7 +5118,7 @@
         <v>46224.887663622685</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5146,7 +5148,7 @@
         <v>212</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>215</v>
@@ -5169,7 +5171,7 @@
         <v>46224.8876609375</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5199,7 +5201,7 @@
         <v>212</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>215</v>
@@ -5222,7 +5224,7 @@
         <v>46224.8876578125</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5252,7 +5254,7 @@
         <v>212</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>218</v>
@@ -5338,7 +5340,7 @@
         <v>46238.48598511574</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5391,7 +5393,7 @@
         <v>46238.48598628472</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5444,7 +5446,7 @@
         <v>46238.485982094906</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5560,7 +5562,7 @@
         <v>46224.888117256945</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5613,7 +5615,7 @@
         <v>46224.88811447917</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5666,7 +5668,7 @@
         <v>46224.88811143518</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5782,7 +5784,7 @@
         <v>46238.48598354167</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5835,7 +5837,7 @@
         <v>46238.48598415509</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5888,7 +5890,7 @@
         <v>46224.88821421296</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -5971,7 +5973,7 @@
         <v>209</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>252</v>
@@ -6004,7 +6006,7 @@
         <v>46224.88831505787</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6034,7 +6036,7 @@
         <v>251</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>254</v>
@@ -6057,7 +6059,7 @@
         <v>46224.88831152778</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6087,7 +6089,7 @@
         <v>251</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>254</v>
@@ -6110,7 +6112,7 @@
         <v>46224.88830864584</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6140,7 +6142,7 @@
         <v>251</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>254</v>
@@ -6226,7 +6228,7 @@
         <v>46224.88840122685</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6254,7 +6256,7 @@
         <v>252</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>261</v>
@@ -6277,7 +6279,7 @@
         <v>46224.88839846065</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6305,7 +6307,7 @@
         <v>252</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>261</v>
@@ -6328,7 +6330,7 @@
         <v>46224.888395601854</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6356,7 +6358,7 @@
         <v>252</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>261</v>
@@ -6489,7 +6491,7 @@
         <v>46224.88851116898</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6519,10 +6521,10 @@
         <v>259</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6542,7 +6544,7 @@
         <v>46224.8885084838</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6572,10 +6574,10 @@
         <v>259</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6595,7 +6597,7 @@
         <v>46224.88850347222</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6625,10 +6627,10 @@
         <v>259</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6711,7 +6713,7 @@
         <v>46224.888643495375</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6739,10 +6741,10 @@
         <v>275</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6762,7 +6764,7 @@
         <v>46224.88864100694</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6790,10 +6792,10 @@
         <v>275</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6813,7 +6815,7 @@
         <v>46224.88863769676</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6841,10 +6843,10 @@
         <v>275</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6927,7 +6929,7 @@
         <v>46224.88880863426</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -6957,10 +6959,10 @@
         <v>281</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -6980,7 +6982,7 @@
         <v>46224.888805462964</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7010,10 +7012,10 @@
         <v>281</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7033,7 +7035,7 @@
         <v>46224.88880255787</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7063,10 +7065,10 @@
         <v>281</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7149,7 +7151,7 @@
         <v>46224.88913273148</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7179,7 +7181,7 @@
         <v>287</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>290</v>
@@ -7202,7 +7204,7 @@
         <v>46224.8891297338</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7232,7 +7234,7 @@
         <v>287</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>290</v>
@@ -7255,7 +7257,7 @@
         <v>46224.88912665509</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7285,7 +7287,7 @@
         <v>287</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>290</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -533,46 +533,46 @@
     <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Bodega ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
+    <t>1216762727441897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma OT 4375 </t>
+  </si>
+  <si>
+    <t>Bodega ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216762727441917</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado OT 4375</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Bodega ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216763159457799</t>
+  </si>
+  <si>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado OT 4375,Preparacion materiales OT 4375,Armado OT 4375</t>
+  </si>
+  <si>
+    <t>1216763159457811</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Caldereria,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216762727441897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma OT 4375 </t>
-  </si>
-  <si>
-    <t>Bodega ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216762727441917</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado OT 4375</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Bodega ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216763159457799</t>
-  </si>
-  <si>
-    <t>Caldereria</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado OT 4375,Preparacion materiales OT 4375,Armado OT 4375</t>
-  </si>
-  <si>
-    <t>1216763159457811</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Caldereria,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1216763159458031</t>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46261.1686759838</v>
+        <v>46262.17361107639</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>164</v>
@@ -4068,8 +4068,8 @@
       <c r="R46" s="5">
         <v>46261</v>
       </c>
-      <c r="S46" s="12" t="s">
-        <v>166</v>
+      <c r="S46" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -4080,7 +4080,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B47" s="9">
         <v>46224.69141809028</v>
@@ -4089,10 +4089,10 @@
         <v>46261.499706030096</v>
       </c>
       <c r="D47" s="9">
-        <v>46261.49972283565</v>
+        <v>46262.17361103009</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
@@ -4125,7 +4125,7 @@
         <v>158</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="9">
         <v>46261</v>
@@ -4133,8 +4133,8 @@
       <c r="R47" s="9">
         <v>46261</v>
       </c>
-      <c r="S47" s="12" t="s">
-        <v>166</v>
+      <c r="S47" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4145,17 +4145,17 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46224.69142430555</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46261.16867167824</v>
+        <v>46262.17361107639</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4188,7 +4188,7 @@
         <v>161</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="5">
         <v>46261</v>
@@ -4196,8 +4196,8 @@
       <c r="R48" s="5">
         <v>46261</v>
       </c>
-      <c r="S48" s="12" t="s">
-        <v>166</v>
+      <c r="S48" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B49" s="9">
         <v>46224.69143046296</v>
@@ -4218,7 +4218,7 @@
         <v>46224.835371608795</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4242,7 +4242,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46224.6914341088</v>
@@ -4271,10 +4271,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I50" s="5">
         <v>46262</v>
@@ -4292,13 +4292,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q50" s="5">
         <v>46266</v>
@@ -4307,7 +4307,7 @@
         <v>46231</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4334,10 +4334,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I51" s="9">
         <v>46267</v>
@@ -4355,13 +4355,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>142</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q51" s="9">
         <v>46273</v>
@@ -4397,10 +4397,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I52" s="5">
         <v>46267</v>
@@ -4450,10 +4450,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I53" s="9">
         <v>46267</v>
@@ -4503,10 +4503,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I54" s="5">
         <v>46267</v>
@@ -4556,10 +4556,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I55" s="9">
         <v>46274</v>
@@ -4577,13 +4577,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>142</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q55" s="9">
         <v>46274</v>
@@ -4619,10 +4619,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I56" s="5">
         <v>46274</v>
@@ -4672,10 +4672,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I57" s="9">
         <v>46274</v>
@@ -4725,10 +4725,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I58" s="5">
         <v>46274</v>
@@ -6872,10 +6872,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I97" s="9">
         <v>46296</v>
@@ -6935,10 +6935,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I98" s="5">
         <v>46296</v>
@@ -6988,10 +6988,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I99" s="9">
         <v>46296</v>
@@ -7041,10 +7041,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I100" s="5">
         <v>46296</v>
@@ -7094,10 +7094,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I101" s="9">
         <v>46297</v>
@@ -7157,10 +7157,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I102" s="5">
         <v>46297</v>
@@ -7210,10 +7210,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I103" s="9">
         <v>46297</v>
@@ -7263,10 +7263,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I104" s="5">
         <v>46297</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -4262,7 +4262,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46261.58820892361</v>
+        <v>46266.16954070602</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>73</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46262.85861983796</v>
+        <v>46266.16994603009</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>117</v>
@@ -4369,8 +4369,8 @@
       <c r="R51" s="9">
         <v>46267</v>
       </c>
-      <c r="S51" s="7" t="s">
-        <v>32</v>
+      <c r="S51" s="12" t="s">
+        <v>179</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -572,10 +572,10 @@
     <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Caldereria,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
+    <t>1216763159458031</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216763159458031</t>
   </si>
   <si>
     <t>1216763159458049</t>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46266.16954070602</v>
+        <v>46267.171079155094</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>73</v>
@@ -4306,8 +4306,8 @@
       <c r="R50" s="5">
         <v>46231</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>179</v>
+      <c r="S50" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4318,7 +4318,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B51" s="9">
         <v>46224.69144137732</v>
@@ -4370,7 +4370,7 @@
         <v>46267</v>
       </c>
       <c r="S51" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46224.88734793982</v>
+        <v>46267.19544847222</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>190</v>
@@ -4591,8 +4591,8 @@
       <c r="R55" s="9">
         <v>46274</v>
       </c>
-      <c r="S55" s="7" t="s">
-        <v>32</v>
+      <c r="S55" s="12" t="s">
+        <v>180</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -4325,7 +4325,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46266.16994603009</v>
+        <v>46273.16861547454</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>117</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46261.499713680554</v>
+        <v>46273.168617442134</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>144</v>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46261.49971425926</v>
+        <v>46273.168612407404</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>144</v>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46261.499714826394</v>
+        <v>46273.16861883102</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>144</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -575,37 +575,37 @@
     <t>1216763159458031</t>
   </si>
   <si>
+    <t>1216763159458049</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado OT 4375,Control de calidad corte Laser OT 4375,Control de calidad Corte plasma OT 4375 ,Check Planos OT 4375,Preparacion materiales OT 4375</t>
+  </si>
+  <si>
+    <t>Armado OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216762727451385</t>
+  </si>
+  <si>
+    <t>Preparacion materiales OT 4375,Control de calidad Mecanizado OT 4375,Control de calidad corte Laser OT 4375,Control de calidad Corte plasma OT 4375 ,Check Planos OT 4375</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Armado OT 4375</t>
+  </si>
+  <si>
+    <t>1216763159476562</t>
+  </si>
+  <si>
+    <t>Preparacion materiales OT 4375,Control de calidad corte Laser OT 4375,Control de calidad Corte plasma OT 4375 ,Control de calidad Mecanizado OT 4375,Check Planos OT 4375</t>
+  </si>
+  <si>
+    <t>1216762958914884</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado OT 4375</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216763159458049</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado OT 4375,Control de calidad corte Laser OT 4375,Control de calidad Corte plasma OT 4375 ,Check Planos OT 4375,Preparacion materiales OT 4375</t>
-  </si>
-  <si>
-    <t>Armado OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216762727451385</t>
-  </si>
-  <si>
-    <t>Preparacion materiales OT 4375,Control de calidad Mecanizado OT 4375,Control de calidad corte Laser OT 4375,Control de calidad Corte plasma OT 4375 ,Check Planos OT 4375</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Armado OT 4375</t>
-  </si>
-  <si>
-    <t>1216763159476562</t>
-  </si>
-  <si>
-    <t>Preparacion materiales OT 4375,Control de calidad corte Laser OT 4375,Control de calidad Corte plasma OT 4375 ,Control de calidad Mecanizado OT 4375,Check Planos OT 4375</t>
-  </si>
-  <si>
-    <t>1216762958914884</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado OT 4375</t>
   </si>
   <si>
     <t>1216762958914899</t>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46273.16861547454</v>
+        <v>46274.14413405093</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>117</v>
@@ -4369,8 +4369,8 @@
       <c r="R51" s="9">
         <v>46267</v>
       </c>
-      <c r="S51" s="12" t="s">
-        <v>180</v>
+      <c r="S51" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B52" s="5">
         <v>46224.69144840278</v>
@@ -4421,10 +4421,10 @@
         <v>117</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B53" s="9">
         <v>46224.691457141205</v>
@@ -4474,10 +4474,10 @@
         <v>117</v>
       </c>
       <c r="O53" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="P53" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="P53" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4487,7 +4487,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B54" s="5">
         <v>46224.69146548611</v>
@@ -4527,10 +4527,10 @@
         <v>117</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4540,17 +4540,17 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B55" s="9">
         <v>46224.691625312495</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46267.19544847222</v>
+        <v>46274.16857871528</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4592,7 +4592,7 @@
         <v>46274</v>
       </c>
       <c r="S55" s="12" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46238.485983136576</v>
+        <v>46274.16858077546</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>144</v>
@@ -4640,7 +4640,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>192</v>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46238.48598453704</v>
+        <v>46274.16858199074</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>144</v>
@@ -4693,7 +4693,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>192</v>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46238.485981562495</v>
+        <v>46274.16858320602</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>144</v>
@@ -4746,7 +4746,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>192</v>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46232.624381828704</v>
+        <v>46274.14175427084</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>212</v>
@@ -5096,8 +5096,8 @@
       <c r="R64" s="5">
         <v>46275</v>
       </c>
-      <c r="S64" s="7" t="s">
-        <v>32</v>
+      <c r="S64" s="12" t="s">
+        <v>190</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -605,76 +605,76 @@
     <t>Control de calidad Armado OT 4375</t>
   </si>
   <si>
+    <t>1216762958914899</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Check Planos OT 4375</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Control de calidad Armado OT 4375</t>
+  </si>
+  <si>
+    <t>1216763050197135</t>
+  </si>
+  <si>
+    <t>1216763050197155</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216763050306173</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe OT 4375,Recepcion motor OT 4375,Recepcion Rodete OT 4375</t>
+  </si>
+  <si>
+    <t>1216763050306185</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe OT 4375</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Bodega:,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216763159677756</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete OT 4375</t>
+  </si>
+  <si>
+    <t>1216763159677776</t>
+  </si>
+  <si>
+    <t>Recepcion motor OT 4375</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Bodega:</t>
+  </si>
+  <si>
+    <t>1216763090891680</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Montaje Rodete OT 4375,Montaje motor OT 4375,Montaje Alabe OT 4375,Revestimiento OT 4375</t>
+  </si>
+  <si>
+    <t>1216763090891690</t>
+  </si>
+  <si>
+    <t>Revestimiento OT 4375</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje Alabe OT 4375</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216762958914899</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Check Planos OT 4375</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Control de calidad Armado OT 4375</t>
-  </si>
-  <si>
-    <t>1216763050197135</t>
-  </si>
-  <si>
-    <t>1216763050197155</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216763050306173</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe OT 4375,Recepcion motor OT 4375,Recepcion Rodete OT 4375</t>
-  </si>
-  <si>
-    <t>1216763050306185</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe OT 4375</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Bodega:,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216763159677756</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete OT 4375</t>
-  </si>
-  <si>
-    <t>1216763159677776</t>
-  </si>
-  <si>
-    <t>Recepcion motor OT 4375</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Bodega:</t>
-  </si>
-  <si>
-    <t>1216763090891680</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Montaje Rodete OT 4375,Montaje motor OT 4375,Montaje Alabe OT 4375,Revestimiento OT 4375</t>
-  </si>
-  <si>
-    <t>1216763090891690</t>
-  </si>
-  <si>
-    <t>Revestimiento OT 4375</t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje Alabe OT 4375</t>
   </si>
   <si>
     <t>1216762727729087</t>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46274.16857871528</v>
+        <v>46275.14471078703</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>189</v>
@@ -4591,8 +4591,8 @@
       <c r="R55" s="9">
         <v>46274</v>
       </c>
-      <c r="S55" s="12" t="s">
-        <v>190</v>
+      <c r="S55" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -4603,7 +4603,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B56" s="5">
         <v>46224.69163763888</v>
@@ -4643,10 +4643,10 @@
         <v>189</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4656,7 +4656,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B57" s="9">
         <v>46224.69164405092</v>
@@ -4696,10 +4696,10 @@
         <v>189</v>
       </c>
       <c r="O57" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="P57" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="P57" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4709,7 +4709,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B58" s="5">
         <v>46224.69164984954</v>
@@ -4749,10 +4749,10 @@
         <v>189</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4762,7 +4762,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B59" s="9">
         <v>46224.69178202546</v>
@@ -4772,7 +4772,7 @@
         <v>46224.83612613426</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -4796,7 +4796,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -4809,7 +4809,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B60" s="5">
         <v>46224.691786446754</v>
@@ -4819,7 +4819,7 @@
         <v>46237.55364837963</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -4846,13 +4846,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>50</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q60" s="5">
         <v>46231</v>
@@ -4872,7 +4872,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B61" s="9">
         <v>46224.69179621528</v>
@@ -4882,7 +4882,7 @@
         <v>46237.55356576389</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -4909,13 +4909,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q61" s="9">
         <v>46231</v>
@@ -4935,7 +4935,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B62" s="5">
         <v>46224.691807152776</v>
@@ -4945,7 +4945,7 @@
         <v>46237.55362008102</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -4972,13 +4972,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>59</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q62" s="5">
         <v>46231</v>
@@ -4998,7 +4998,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B63" s="9">
         <v>46224.69181694444</v>
@@ -5008,7 +5008,7 @@
         <v>46232.60338635417</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>25</v>
@@ -5032,7 +5032,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5045,7 +5045,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B64" s="5">
         <v>46224.69182049768</v>
@@ -5055,7 +5055,7 @@
         <v>46274.14175427084</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5082,13 +5082,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>142</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q64" s="5">
         <v>46281</v>
@@ -5097,7 +5097,7 @@
         <v>46275</v>
       </c>
       <c r="S64" s="12" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>144</v>
@@ -5198,7 +5198,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>144</v>
@@ -5251,7 +5251,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>144</v>
@@ -5304,7 +5304,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>221</v>
@@ -5526,7 +5526,7 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>232</v>
@@ -5748,13 +5748,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>242</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q76" s="5">
         <v>46288</v>
@@ -5970,7 +5970,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>142</v>
@@ -6192,7 +6192,7 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>258</v>
